--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ53"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135825124</v>
+        <v>135828229</v>
       </c>
       <c r="B3" t="n">
-        <v>79140</v>
+        <v>83453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,34 +804,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741095</v>
+        <v>741140</v>
       </c>
       <c r="R3" t="n">
-        <v>7294406</v>
+        <v>7294373</v>
       </c>
       <c r="S3" t="n">
         <v>6</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,74 +882,72 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825124</t>
+          <t>https://artportalen.se/Sighting/135828229</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131421827</v>
+        <v>135825124</v>
       </c>
       <c r="B4" t="n">
-        <v>79442</v>
+        <v>79140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>639</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grenlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Evernia mesomorpha</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741351</v>
+        <v>741095</v>
       </c>
       <c r="R4" t="n">
-        <v>7294438</v>
+        <v>7294406</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,12 +971,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,7 +995,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,16 +1012,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421827</t>
+          <t>https://artportalen.se/Sighting/135825124</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135828232</v>
+        <v>131421827</v>
       </c>
       <c r="B5" t="n">
-        <v>89369</v>
+        <v>79442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,45 +1029,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>816</v>
+        <v>639</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smultronkantarell</t>
+          <t>Grenlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aphroditeola olida</t>
+          <t>Evernia mesomorpha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Nyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741170</v>
+        <v>741351</v>
       </c>
       <c r="R5" t="n">
-        <v>7294518</v>
+        <v>7294438</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,22 +1086,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>20:26</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>20:26</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,73 +1104,76 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828232</t>
+          <t>https://artportalen.se/Sighting/131421827</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135825122</v>
+        <v>135828232</v>
       </c>
       <c r="B6" t="n">
-        <v>92024</v>
+        <v>89369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>816</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741077</v>
+        <v>741170</v>
       </c>
       <c r="R6" t="n">
-        <v>7294449</v>
+        <v>7294518</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1213,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1215,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,30 +1228,35 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825122</t>
+          <t>https://artportalen.se/Sighting/135828232</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135828223</v>
+        <v>135825122</v>
       </c>
       <c r="B7" t="n">
-        <v>87497</v>
+        <v>92024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,45 +1264,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3690</v>
+        <v>3242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Soop</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741105</v>
+        <v>741077</v>
       </c>
       <c r="R7" t="n">
-        <v>7294388</v>
+        <v>7294449</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1337,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1336,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,35 +1349,30 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828223</t>
+          <t>https://artportalen.se/Sighting/135825122</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110044413</v>
+        <v>135828223</v>
       </c>
       <c r="B8" t="n">
-        <v>93189</v>
+        <v>87497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,37 +1380,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741238</v>
+        <v>741105</v>
       </c>
       <c r="R8" t="n">
-        <v>7294539</v>
+        <v>7294388</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,12 +1445,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,33 +1469,39 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044413</t>
+          <t>https://artportalen.se/Sighting/135828223</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135825131</v>
+        <v>110044413</v>
       </c>
       <c r="B9" t="n">
-        <v>93391</v>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,17 +1529,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741193</v>
+        <v>741238</v>
       </c>
       <c r="R9" t="n">
-        <v>7294441</v>
+        <v>7294539</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,22 +1563,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>20:12</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>20:12</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,27 +1583,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825131</t>
+          <t>https://artportalen.se/Sighting/110044413</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110044367</v>
+        <v>135825131</v>
       </c>
       <c r="B10" t="n">
-        <v>93191</v>
+        <v>93391</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,37 +1611,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741263</v>
+        <v>741193</v>
       </c>
       <c r="R10" t="n">
-        <v>7294543</v>
+        <v>7294441</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1664,12 +1665,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,24 +1695,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044367</t>
+          <t>https://artportalen.se/Sighting/135825131</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110044387</v>
+        <v>110044367</v>
       </c>
       <c r="B11" t="n">
         <v>93191</v>
@@ -1736,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741505</v>
+        <v>741263</v>
       </c>
       <c r="R11" t="n">
-        <v>7294450</v>
+        <v>7294543</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,13 +1808,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044387</t>
+          <t>https://artportalen.se/Sighting/110044367</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129000538</v>
+        <v>110044387</v>
       </c>
       <c r="B12" t="n">
         <v>93191</v>
@@ -1831,21 +1842,17 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741402</v>
+        <v>741505</v>
       </c>
       <c r="R12" t="n">
-        <v>7294418</v>
+        <v>7294450</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,17 +1879,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,27 +1899,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000538</t>
+          <t>https://artportalen.se/Sighting/110044387</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110044379</v>
+        <v>129000538</v>
       </c>
       <c r="B13" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1925,34 +1927,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741287</v>
+        <v>741402</v>
       </c>
       <c r="R13" t="n">
-        <v>7294517</v>
+        <v>7294418</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,12 +1985,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,24 +2010,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044379</t>
+          <t>https://artportalen.se/Sighting/129000538</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129000536</v>
+        <v>110044379</v>
       </c>
       <c r="B14" t="n">
         <v>93197</v>
@@ -2044,21 +2055,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741464</v>
+        <v>741287</v>
       </c>
       <c r="R14" t="n">
-        <v>7294503</v>
+        <v>7294517</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,17 +2092,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,27 +2112,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000536</t>
+          <t>https://artportalen.se/Sighting/110044379</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135825120</v>
+        <v>129000536</v>
       </c>
       <c r="B15" t="n">
-        <v>93400</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,20 +2157,24 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741122</v>
+        <v>741464</v>
       </c>
       <c r="R15" t="n">
-        <v>7294512</v>
+        <v>7294503</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2192,22 +2198,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>18:58</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>18:58</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2222,27 +2223,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825120</t>
+          <t>https://artportalen.se/Sighting/129000536</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135825130</v>
+        <v>135825120</v>
       </c>
       <c r="B16" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741149</v>
+        <v>741122</v>
       </c>
       <c r="R16" t="n">
-        <v>7294363</v>
+        <v>7294512</v>
       </c>
       <c r="S16" t="n">
         <v>6</v>
@@ -2309,7 +2310,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2319,7 +2320,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,13 +2346,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825130</t>
+          <t>https://artportalen.se/Sighting/135825120</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135825132</v>
+        <v>135825130</v>
       </c>
       <c r="B17" t="n">
         <v>93399</v>
@@ -2386,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741186</v>
+        <v>741149</v>
       </c>
       <c r="R17" t="n">
-        <v>7294441</v>
+        <v>7294363</v>
       </c>
       <c r="S17" t="n">
         <v>6</v>
@@ -2421,7 +2422,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2431,7 +2432,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2457,16 +2458,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825132</t>
+          <t>https://artportalen.se/Sighting/135825130</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135828222</v>
+        <v>135825132</v>
       </c>
       <c r="B18" t="n">
-        <v>93400</v>
+        <v>93399</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2492,22 +2493,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741097</v>
+        <v>741186</v>
       </c>
       <c r="R18" t="n">
-        <v>7294374</v>
+        <v>7294441</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2536,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2546,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2555,36 +2553,30 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828222</t>
+          <t>https://artportalen.se/Sighting/135825132</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135828226</v>
+        <v>135828222</v>
       </c>
       <c r="B19" t="n">
         <v>93400</v>
@@ -2622,13 +2614,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741113</v>
+        <v>741097</v>
       </c>
       <c r="R19" t="n">
-        <v>7294382</v>
+        <v>7294374</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2657,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2667,7 +2659,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2699,16 +2691,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828226</t>
+          <t>https://artportalen.se/Sighting/135828222</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129000539</v>
+        <v>135828226</v>
       </c>
       <c r="B20" t="n">
-        <v>93209</v>
+        <v>93400</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,41 +2708,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741260</v>
+        <v>741113</v>
       </c>
       <c r="R20" t="n">
-        <v>7294367</v>
+        <v>7294382</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2774,17 +2765,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2793,30 +2789,36 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000539</t>
+          <t>https://artportalen.se/Sighting/135828226</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129000541</v>
+        <v>129000539</v>
       </c>
       <c r="B21" t="n">
         <v>93209</v>
@@ -2855,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741209</v>
+        <v>741260</v>
       </c>
       <c r="R21" t="n">
-        <v>7294469</v>
+        <v>7294367</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2921,50 +2923,58 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000541</t>
+          <t>https://artportalen.se/Sighting/129000539</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135825125</v>
+        <v>129000541</v>
       </c>
       <c r="B22" t="n">
-        <v>93429</v>
+        <v>93209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741107</v>
+        <v>741209</v>
       </c>
       <c r="R22" t="n">
-        <v>7294391</v>
+        <v>7294469</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2988,27 +2998,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>19:44</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>19:44</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>och äldre fruktkropp</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3023,27 +3023,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825125</t>
+          <t>https://artportalen.se/Sighting/129000541</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135825123</v>
+        <v>135825125</v>
       </c>
       <c r="B23" t="n">
-        <v>91461</v>
+        <v>93429</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3051,23 +3051,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5685</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3075,13 +3071,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>741088</v>
+        <v>741107</v>
       </c>
       <c r="R23" t="n">
         <v>7294391</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3110,7 +3106,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3120,7 +3116,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>och äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3146,58 +3147,54 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825123</t>
+          <t>https://artportalen.se/Sighting/135825125</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129000537</v>
+        <v>135825123</v>
       </c>
       <c r="B24" t="n">
-        <v>93235</v>
+        <v>91461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>5685</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741430</v>
+        <v>741088</v>
       </c>
       <c r="R24" t="n">
-        <v>7294484</v>
+        <v>7294391</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3221,17 +3218,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3246,65 +3248,69 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000537</t>
+          <t>https://artportalen.se/Sighting/135825123</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131421831</v>
+        <v>129000537</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>93235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741264</v>
+        <v>741430</v>
       </c>
       <c r="R25" t="n">
-        <v>7294336</v>
+        <v>7294484</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3328,12 +3334,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,49 +3359,49 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421831</t>
+          <t>https://artportalen.se/Sighting/129000537</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131421828</v>
+        <v>131421831</v>
       </c>
       <c r="B26" t="n">
-        <v>79397</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3400,10 +3411,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>741410</v>
+        <v>741264</v>
       </c>
       <c r="R26" t="n">
-        <v>7294501</v>
+        <v>7294336</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3461,16 +3472,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421828</t>
+          <t>https://artportalen.se/Sighting/131421831</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135828228</v>
+        <v>131421828</v>
       </c>
       <c r="B27" t="n">
-        <v>79498</v>
+        <v>79397</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3496,19 +3507,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>741122</v>
+        <v>741410</v>
       </c>
       <c r="R27" t="n">
-        <v>7294378</v>
+        <v>7294501</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3535,22 +3543,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>19:58</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>19:58</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3559,89 +3557,71 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828228</t>
+          <t>https://artportalen.se/Sighting/131421828</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135825128</v>
+        <v>135828228</v>
       </c>
       <c r="B28" t="n">
-        <v>78876</v>
+        <v>79498</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741118</v>
+        <v>741122</v>
       </c>
       <c r="R28" t="n">
-        <v>7294382</v>
+        <v>7294378</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3673,7 +3653,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3683,7 +3663,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3692,33 +3672,54 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825128</t>
+          <t>https://artportalen.se/Sighting/135828228</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129000543</v>
+        <v>135825128</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>78876</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3726,41 +3727,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741337</v>
+        <v>741118</v>
       </c>
       <c r="R29" t="n">
-        <v>7294536</v>
+        <v>7294382</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3784,17 +3781,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3809,27 +3811,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000543</t>
+          <t>https://artportalen.se/Sighting/135825128</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129000542</v>
+        <v>129000543</v>
       </c>
       <c r="B30" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3837,21 +3839,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3865,10 +3867,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>741225</v>
+        <v>741337</v>
       </c>
       <c r="R30" t="n">
-        <v>7294470</v>
+        <v>7294536</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3931,13 +3933,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000542</t>
+          <t>https://artportalen.se/Sighting/129000543</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129000544</v>
+        <v>129000542</v>
       </c>
       <c r="B31" t="n">
         <v>79946</v>
@@ -3976,10 +3978,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>741341</v>
+        <v>741225</v>
       </c>
       <c r="R31" t="n">
-        <v>7294535</v>
+        <v>7294470</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4042,16 +4044,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000544</t>
+          <t>https://artportalen.se/Sighting/129000542</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135825121</v>
+        <v>129000544</v>
       </c>
       <c r="B32" t="n">
-        <v>80093</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4076,20 +4078,24 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>741110</v>
+        <v>741341</v>
       </c>
       <c r="R32" t="n">
-        <v>7294497</v>
+        <v>7294535</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4113,22 +4119,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>19:03</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>19:03</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4143,27 +4144,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825121</t>
+          <t>https://artportalen.se/Sighting/129000544</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135825127</v>
+        <v>135825121</v>
       </c>
       <c r="B33" t="n">
-        <v>78477</v>
+        <v>80093</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4171,21 +4172,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4195,13 +4196,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741118</v>
+        <v>741110</v>
       </c>
       <c r="R33" t="n">
-        <v>7294382</v>
+        <v>7294497</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4230,7 +4231,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4240,7 +4241,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4266,16 +4267,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825127</t>
+          <t>https://artportalen.se/Sighting/135825121</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131421821</v>
+        <v>135825127</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>78477</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4283,37 +4284,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741194</v>
+        <v>741118</v>
       </c>
       <c r="R34" t="n">
-        <v>7294285</v>
+        <v>7294382</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4337,17 +4338,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och gamla, tall</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4373,13 +4379,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421821</t>
+          <t>https://artportalen.se/Sighting/135825127</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131421823</v>
+        <v>131421821</v>
       </c>
       <c r="B35" t="n">
         <v>57975</v>
@@ -4414,10 +4420,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741167</v>
+        <v>741194</v>
       </c>
       <c r="R35" t="n">
-        <v>7294289</v>
+        <v>7294285</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4454,7 +4460,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Nya och gamla ringhack rikligt, tall</t>
+          <t>Ringhack färska och gamla, tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4480,13 +4486,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421823</t>
+          <t>https://artportalen.se/Sighting/131421821</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131421824</v>
+        <v>131421823</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -4521,10 +4527,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741275</v>
+        <v>741167</v>
       </c>
       <c r="R36" t="n">
-        <v>7294333</v>
+        <v>7294289</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4561,7 +4567,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gamla och nya ringhack, tallhed.</t>
+          <t>Nya och gamla ringhack rikligt, tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4587,13 +4593,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421824</t>
+          <t>https://artportalen.se/Sighting/131421823</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131421825</v>
+        <v>131421824</v>
       </c>
       <c r="B37" t="n">
         <v>57975</v>
@@ -4628,10 +4634,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>741401</v>
+        <v>741275</v>
       </c>
       <c r="R37" t="n">
-        <v>7294510</v>
+        <v>7294333</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4668,7 +4674,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Nya och gamla ringhack, rikligt, tall.</t>
+          <t>Gamla och nya ringhack, tallhed.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4694,13 +4700,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421825</t>
+          <t>https://artportalen.se/Sighting/131421824</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132365365</v>
+        <v>131421825</v>
       </c>
       <c r="B38" t="n">
         <v>57975</v>
@@ -4729,27 +4735,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Väster om Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741417</v>
+        <v>741401</v>
       </c>
       <c r="R38" t="n">
-        <v>7294498</v>
+        <v>7294510</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4783,7 +4781,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Nya och gamla ringhack, rikligt, tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4798,24 +4796,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365365</t>
+          <t>https://artportalen.se/Sighting/131421825</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132365428</v>
+        <v>132365365</v>
       </c>
       <c r="B39" t="n">
         <v>57975</v>
@@ -4858,10 +4856,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741294</v>
+        <v>741417</v>
       </c>
       <c r="R39" t="n">
-        <v>7294330</v>
+        <v>7294498</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4898,7 +4896,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Flera ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4924,13 +4922,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365428</t>
+          <t>https://artportalen.se/Sighting/132365365</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132365494</v>
+        <v>132365428</v>
       </c>
       <c r="B40" t="n">
         <v>57975</v>
@@ -4963,20 +4961,20 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>SydVäst om Sikträsket, Nb</t>
+          <t>Väster om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741247</v>
+        <v>741294</v>
       </c>
       <c r="R40" t="n">
-        <v>7294318</v>
+        <v>7294330</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5013,14 +5011,14 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Flertalet ringhack på träd i direkt anslutning till bohålet</t>
+          <t>Flera ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>
@@ -5039,16 +5037,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365494</t>
+          <t>https://artportalen.se/Sighting/132365428</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135825133</v>
+        <v>132365494</v>
       </c>
       <c r="B41" t="n">
-        <v>58006</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5074,19 +5072,27 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>SydVäst om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741176</v>
+        <v>741247</v>
       </c>
       <c r="R41" t="n">
-        <v>7294442</v>
+        <v>7294318</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5110,34 +5116,24 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>20:17</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>20:17</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack</t>
+          <t>Flertalet ringhack på träd i direkt anslutning till bohålet</t>
         </is>
       </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
@@ -5145,24 +5141,24 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825133</t>
+          <t>https://artportalen.se/Sighting/132365494</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135828227</v>
+        <v>135825133</v>
       </c>
       <c r="B42" t="n">
         <v>58006</v>
@@ -5191,24 +5187,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>741122</v>
+        <v>741176</v>
       </c>
       <c r="R42" t="n">
-        <v>7294378</v>
+        <v>7294442</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5240,7 +5228,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5250,12 +5238,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5266,48 +5254,28 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828227</t>
+          <t>https://artportalen.se/Sighting/135825133</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135828230</v>
+        <v>135828227</v>
       </c>
       <c r="B43" t="n">
         <v>58006</v>
@@ -5340,7 +5308,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5350,10 +5318,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>741155</v>
+        <v>741122</v>
       </c>
       <c r="R43" t="n">
-        <v>7294379</v>
+        <v>7294378</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5385,7 +5353,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5395,12 +5363,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5446,13 +5414,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828230</t>
+          <t>https://artportalen.se/Sighting/135828227</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135828231</v>
+        <v>135828230</v>
       </c>
       <c r="B44" t="n">
         <v>58006</v>
@@ -5485,7 +5453,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5495,13 +5463,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>741186</v>
+        <v>741155</v>
       </c>
       <c r="R44" t="n">
-        <v>7294423</v>
+        <v>7294379</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5530,7 +5498,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5540,12 +5508,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5560,6 +5528,21 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5576,56 +5559,59 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828231</t>
+          <t>https://artportalen.se/Sighting/135828230</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135825126</v>
+        <v>135828231</v>
       </c>
       <c r="B45" t="n">
-        <v>57193</v>
+        <v>58006</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>741114</v>
+        <v>741186</v>
       </c>
       <c r="R45" t="n">
-        <v>7294391</v>
+        <v>7294423</v>
       </c>
       <c r="S45" t="n">
         <v>6</v>
@@ -5657,7 +5643,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5667,7 +5653,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5678,77 +5669,79 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825126</t>
+          <t>https://artportalen.se/Sighting/135828231</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135857317</v>
+        <v>135825126</v>
       </c>
       <c r="B46" t="n">
-        <v>58167</v>
+        <v>57193</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>741177</v>
+        <v>741114</v>
       </c>
       <c r="R46" t="n">
-        <v>7294392</v>
+        <v>7294391</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5777,7 +5770,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5787,12 +5780,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>20:09</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Lockläten</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5803,71 +5791,74 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135857317</t>
+          <t>https://artportalen.se/Sighting/135825126</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131421826</v>
+        <v>135857317</v>
       </c>
       <c r="B47" t="n">
-        <v>58131</v>
+        <v>58167</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>741150</v>
+        <v>741177</v>
       </c>
       <c r="R47" t="n">
-        <v>7294265</v>
+        <v>7294392</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5894,12 +5885,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Lockläten</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5910,28 +5916,33 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421826</t>
+          <t>https://artportalen.se/Sighting/135857317</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132365028</v>
+        <v>131421826</v>
       </c>
       <c r="B48" t="n">
         <v>58131</v>
@@ -5959,36 +5970,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>SydVäst om Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>741151</v>
+        <v>741150</v>
       </c>
       <c r="R48" t="n">
-        <v>7294262</v>
+        <v>7294265</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6015,19 +6010,9 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6042,44 +6027,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365028</t>
+          <t>https://artportalen.se/Sighting/131421826</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>110044410</v>
+        <v>132365028</v>
       </c>
       <c r="B49" t="n">
-        <v>58057</v>
+        <v>58131</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103031</v>
+        <v>103023</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6087,17 +6072,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>SydVäst om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>741267</v>
+        <v>741151</v>
       </c>
       <c r="R49" t="n">
-        <v>7294536</v>
+        <v>7294262</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6124,12 +6125,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6144,69 +6155,65 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044410</t>
+          <t>https://artportalen.se/Sighting/132365028</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135828221</v>
+        <v>110044410</v>
       </c>
       <c r="B50" t="n">
-        <v>98204</v>
+        <v>58057</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>741098</v>
+        <v>741267</v>
       </c>
       <c r="R50" t="n">
-        <v>7294366</v>
+        <v>7294536</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6230,22 +6237,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>19:35</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>19:35</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6254,81 +6251,75 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828221</t>
+          <t>https://artportalen.se/Sighting/110044410</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129000540</v>
+        <v>135828221</v>
       </c>
       <c r="B51" t="n">
-        <v>79085</v>
+        <v>98204</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>741238</v>
+        <v>741098</v>
       </c>
       <c r="R51" t="n">
-        <v>7294334</v>
+        <v>7294366</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6352,17 +6343,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6371,33 +6367,39 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000540</t>
+          <t>https://artportalen.se/Sighting/135828221</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135828224</v>
+        <v>129000540</v>
       </c>
       <c r="B52" t="n">
-        <v>79232</v>
+        <v>79085</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6422,23 +6424,24 @@
           <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>741114</v>
+        <v>741238</v>
       </c>
       <c r="R52" t="n">
-        <v>7294379</v>
+        <v>7294334</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6462,22 +6465,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>19:50</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>19:50</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6486,39 +6484,33 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828224</t>
+          <t>https://artportalen.se/Sighting/129000540</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135825134</v>
+        <v>135828224</v>
       </c>
       <c r="B53" t="n">
-        <v>79496</v>
+        <v>79232</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6526,37 +6518,40 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>260591</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>741168</v>
+        <v>741114</v>
       </c>
       <c r="R53" t="n">
-        <v>7294460</v>
+        <v>7294379</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6585,7 +6580,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6595,7 +6590,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6604,22 +6599,140 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828224</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135825134</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79496</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Sv Sikträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>741168</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7294460</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135825134</t>
         </is>
@@ -6679,6 +6792,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>135825122</v>
       </c>
       <c r="B7" t="n">
-        <v>92024</v>
+        <v>92027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>135825122</v>
       </c>
       <c r="B7" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ54"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,51 +1253,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135825122</v>
+        <v>136759763</v>
       </c>
       <c r="B7" t="n">
-        <v>92028</v>
+        <v>89371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3242</v>
+        <v>816</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741077</v>
+        <v>741169</v>
       </c>
       <c r="R7" t="n">
-        <v>7294449</v>
+        <v>7294502</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1321,22 +1322,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,34 +1351,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825122</t>
+          <t>https://artportalen.se/Sighting/136759763</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135828223</v>
+        <v>135825122</v>
       </c>
       <c r="B8" t="n">
-        <v>87497</v>
+        <v>92028</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,45 +1385,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3690</v>
+        <v>3242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Soop</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741105</v>
+        <v>741077</v>
       </c>
       <c r="R8" t="n">
-        <v>7294388</v>
+        <v>7294449</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,35 +1470,30 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828223</t>
+          <t>https://artportalen.se/Sighting/135825122</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110044413</v>
+        <v>135828223</v>
       </c>
       <c r="B9" t="n">
-        <v>93189</v>
+        <v>87497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,37 +1501,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741238</v>
+        <v>741105</v>
       </c>
       <c r="R9" t="n">
-        <v>7294539</v>
+        <v>7294388</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1563,12 +1566,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,33 +1590,39 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044413</t>
+          <t>https://artportalen.se/Sighting/135828223</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135825131</v>
+        <v>110044413</v>
       </c>
       <c r="B10" t="n">
-        <v>93391</v>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,17 +1650,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741193</v>
+        <v>741238</v>
       </c>
       <c r="R10" t="n">
-        <v>7294441</v>
+        <v>7294539</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,22 +1684,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>20:12</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>20:12</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,27 +1704,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825131</t>
+          <t>https://artportalen.se/Sighting/110044413</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110044367</v>
+        <v>135825131</v>
       </c>
       <c r="B11" t="n">
-        <v>93191</v>
+        <v>93391</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,37 +1732,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741263</v>
+        <v>741193</v>
       </c>
       <c r="R11" t="n">
-        <v>7294543</v>
+        <v>7294441</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,12 +1786,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,27 +1816,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044367</t>
+          <t>https://artportalen.se/Sighting/135825131</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110044387</v>
+        <v>136759782</v>
       </c>
       <c r="B12" t="n">
-        <v>93191</v>
+        <v>93396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,37 +1844,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741505</v>
+        <v>741380</v>
       </c>
       <c r="R12" t="n">
-        <v>7294450</v>
+        <v>7294626</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1879,12 +1902,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,24 +1937,24 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044387</t>
+          <t>https://artportalen.se/Sighting/136759782</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129000538</v>
+        <v>110044367</v>
       </c>
       <c r="B13" t="n">
         <v>93191</v>
@@ -1944,21 +1982,17 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741402</v>
+        <v>741263</v>
       </c>
       <c r="R13" t="n">
-        <v>7294418</v>
+        <v>7294543</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1985,17 +2019,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,27 +2039,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000538</t>
+          <t>https://artportalen.se/Sighting/110044367</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110044379</v>
+        <v>110044387</v>
       </c>
       <c r="B14" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,21 +2067,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2062,10 +2091,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741287</v>
+        <v>741505</v>
       </c>
       <c r="R14" t="n">
-        <v>7294517</v>
+        <v>7294450</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2123,16 +2152,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044379</t>
+          <t>https://artportalen.se/Sighting/110044387</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129000536</v>
+        <v>129000538</v>
       </c>
       <c r="B15" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,21 +2169,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2168,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741464</v>
+        <v>741402</v>
       </c>
       <c r="R15" t="n">
-        <v>7294503</v>
+        <v>7294418</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2234,16 +2263,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000536</t>
+          <t>https://artportalen.se/Sighting/129000538</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135825120</v>
+        <v>136759889</v>
       </c>
       <c r="B16" t="n">
-        <v>93400</v>
+        <v>93398</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2251,37 +2280,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741122</v>
+        <v>741177</v>
       </c>
       <c r="R16" t="n">
-        <v>7294512</v>
+        <v>7294519</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2305,22 +2338,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2335,27 +2373,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825120</t>
+          <t>https://artportalen.se/Sighting/136759889</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135825130</v>
+        <v>110044379</v>
       </c>
       <c r="B17" t="n">
-        <v>93399</v>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2383,17 +2421,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741149</v>
+        <v>741287</v>
       </c>
       <c r="R17" t="n">
-        <v>7294363</v>
+        <v>7294517</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2417,22 +2455,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>20:05</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>20:05</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2447,27 +2475,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825130</t>
+          <t>https://artportalen.se/Sighting/110044379</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135825132</v>
+        <v>129000536</v>
       </c>
       <c r="B18" t="n">
-        <v>93399</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2492,20 +2520,24 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741186</v>
+        <v>741464</v>
       </c>
       <c r="R18" t="n">
-        <v>7294441</v>
+        <v>7294503</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2529,22 +2561,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>20:14</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>20:14</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,24 +2586,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825132</t>
+          <t>https://artportalen.se/Sighting/129000536</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135828222</v>
+        <v>135825120</v>
       </c>
       <c r="B19" t="n">
         <v>93400</v>
@@ -2605,22 +2632,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741097</v>
+        <v>741122</v>
       </c>
       <c r="R19" t="n">
-        <v>7294374</v>
+        <v>7294512</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,7 +2673,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2659,7 +2683,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2668,39 +2692,33 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828222</t>
+          <t>https://artportalen.se/Sighting/135825120</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135828226</v>
+        <v>135825130</v>
       </c>
       <c r="B20" t="n">
-        <v>93400</v>
+        <v>93399</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,22 +2744,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741113</v>
+        <v>741149</v>
       </c>
       <c r="R20" t="n">
-        <v>7294382</v>
+        <v>7294363</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2770,7 +2785,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,7 +2795,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2789,39 +2804,33 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828226</t>
+          <t>https://artportalen.se/Sighting/135825130</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129000539</v>
+        <v>135825132</v>
       </c>
       <c r="B21" t="n">
-        <v>93209</v>
+        <v>93399</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2829,41 +2838,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741260</v>
+        <v>741186</v>
       </c>
       <c r="R21" t="n">
-        <v>7294367</v>
+        <v>7294441</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2887,17 +2892,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,27 +2922,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000539</t>
+          <t>https://artportalen.se/Sighting/135825132</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129000541</v>
+        <v>135828222</v>
       </c>
       <c r="B22" t="n">
-        <v>93209</v>
+        <v>93400</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2940,41 +2950,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741209</v>
+        <v>741097</v>
       </c>
       <c r="R22" t="n">
-        <v>7294469</v>
+        <v>7294374</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2998,17 +3007,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3017,67 +3031,80 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000541</t>
+          <t>https://artportalen.se/Sighting/135828222</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135825125</v>
+        <v>135828226</v>
       </c>
       <c r="B23" t="n">
-        <v>93429</v>
+        <v>93400</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>741107</v>
+        <v>741113</v>
       </c>
       <c r="R23" t="n">
-        <v>7294391</v>
+        <v>7294382</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3106,7 +3133,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3116,12 +3143,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>och äldre fruktkropp</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3130,71 +3152,81 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825125</t>
+          <t>https://artportalen.se/Sighting/135828226</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135825123</v>
+        <v>136759878</v>
       </c>
       <c r="B24" t="n">
-        <v>91461</v>
+        <v>93404</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741088</v>
+        <v>741257</v>
       </c>
       <c r="R24" t="n">
-        <v>7294391</v>
+        <v>7294543</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3218,22 +3250,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3248,27 +3285,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825123</t>
+          <t>https://artportalen.se/Sighting/136759878</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129000537</v>
+        <v>136759879</v>
       </c>
       <c r="B25" t="n">
-        <v>93235</v>
+        <v>93404</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,21 +3313,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3304,13 +3341,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741430</v>
+        <v>741265</v>
       </c>
       <c r="R25" t="n">
-        <v>7294484</v>
+        <v>7294548</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3334,12 +3371,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3370,54 +3417,58 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000537</t>
+          <t>https://artportalen.se/Sighting/136759879</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131421831</v>
+        <v>129000539</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>93209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>741264</v>
+        <v>741260</v>
       </c>
       <c r="R26" t="n">
-        <v>7294336</v>
+        <v>7294367</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3441,12 +3492,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,65 +3517,69 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421831</t>
+          <t>https://artportalen.se/Sighting/129000539</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131421828</v>
+        <v>129000541</v>
       </c>
       <c r="B27" t="n">
-        <v>79397</v>
+        <v>93209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6434</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>741410</v>
+        <v>741209</v>
       </c>
       <c r="R27" t="n">
-        <v>7294501</v>
+        <v>7294469</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3543,12 +3603,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3563,68 +3628,65 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421828</t>
+          <t>https://artportalen.se/Sighting/129000541</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135828228</v>
+        <v>136760079</v>
       </c>
       <c r="B28" t="n">
-        <v>79498</v>
+        <v>93430</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6434</v>
+        <v>5448</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741122</v>
+        <v>741170</v>
       </c>
       <c r="R28" t="n">
-        <v>7294378</v>
+        <v>7294500</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3648,22 +3710,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>19:58</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>19:58</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3672,78 +3729,53 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828228</t>
+          <t>https://artportalen.se/Sighting/136760079</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135825128</v>
+        <v>135825125</v>
       </c>
       <c r="B29" t="n">
-        <v>78876</v>
+        <v>93429</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>5449</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3751,10 +3783,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741118</v>
+        <v>741107</v>
       </c>
       <c r="R29" t="n">
-        <v>7294382</v>
+        <v>7294391</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3786,7 +3818,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3796,7 +3828,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>och äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3822,58 +3859,54 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825128</t>
+          <t>https://artportalen.se/Sighting/135825125</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129000543</v>
+        <v>135825123</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>91461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>5685</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>741337</v>
+        <v>741088</v>
       </c>
       <c r="R30" t="n">
-        <v>7294536</v>
+        <v>7294391</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3897,17 +3930,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3922,27 +3960,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000543</t>
+          <t>https://artportalen.se/Sighting/135825123</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129000542</v>
+        <v>129000537</v>
       </c>
       <c r="B31" t="n">
-        <v>79946</v>
+        <v>93235</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3950,21 +3988,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3978,10 +4016,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>741225</v>
+        <v>741430</v>
       </c>
       <c r="R31" t="n">
-        <v>7294470</v>
+        <v>7294484</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4044,58 +4082,54 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000542</t>
+          <t>https://artportalen.se/Sighting/129000537</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129000544</v>
+        <v>131421831</v>
       </c>
       <c r="B32" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>741341</v>
+        <v>741264</v>
       </c>
       <c r="R32" t="n">
-        <v>7294535</v>
+        <v>7294336</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4119,17 +4153,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4144,62 +4173,62 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000544</t>
+          <t>https://artportalen.se/Sighting/131421831</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135825121</v>
+        <v>131421828</v>
       </c>
       <c r="B33" t="n">
-        <v>80093</v>
+        <v>79397</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741110</v>
+        <v>741410</v>
       </c>
       <c r="R33" t="n">
-        <v>7294497</v>
+        <v>7294501</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4226,22 +4255,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>19:03</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>19:03</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4267,54 +4286,57 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825121</t>
+          <t>https://artportalen.se/Sighting/131421828</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135825127</v>
+        <v>135828228</v>
       </c>
       <c r="B34" t="n">
-        <v>78477</v>
+        <v>79498</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>6434</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741118</v>
+        <v>741122</v>
       </c>
       <c r="R34" t="n">
-        <v>7294382</v>
+        <v>7294378</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4343,7 +4365,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4353,7 +4375,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4362,33 +4384,54 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825127</t>
+          <t>https://artportalen.se/Sighting/135828228</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131421821</v>
+        <v>135825128</v>
       </c>
       <c r="B35" t="n">
-        <v>57975</v>
+        <v>78876</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4396,34 +4439,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741194</v>
+        <v>741118</v>
       </c>
       <c r="R35" t="n">
-        <v>7294285</v>
+        <v>7294382</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4450,17 +4493,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack färska och gamla, tall</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4486,16 +4534,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421821</t>
+          <t>https://artportalen.se/Sighting/135825128</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131421823</v>
+        <v>129000543</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4503,37 +4551,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741167</v>
+        <v>741337</v>
       </c>
       <c r="R36" t="n">
-        <v>7294289</v>
+        <v>7294536</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4557,17 +4609,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Nya och gamla ringhack rikligt, tall</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4582,27 +4634,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421823</t>
+          <t>https://artportalen.se/Sighting/129000543</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131421824</v>
+        <v>129000542</v>
       </c>
       <c r="B37" t="n">
-        <v>57975</v>
+        <v>79946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4610,37 +4662,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>741275</v>
+        <v>741225</v>
       </c>
       <c r="R37" t="n">
-        <v>7294333</v>
+        <v>7294470</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4664,17 +4720,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gamla och nya ringhack, tallhed.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4689,27 +4745,27 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421824</t>
+          <t>https://artportalen.se/Sighting/129000542</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131421825</v>
+        <v>129000544</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4717,37 +4773,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741401</v>
+        <v>741341</v>
       </c>
       <c r="R38" t="n">
-        <v>7294510</v>
+        <v>7294535</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4771,17 +4831,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Nya och gamla ringhack, rikligt, tall.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4796,27 +4856,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421825</t>
+          <t>https://artportalen.se/Sighting/129000544</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132365365</v>
+        <v>135825121</v>
       </c>
       <c r="B39" t="n">
-        <v>57975</v>
+        <v>80093</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4824,45 +4884,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Väster om Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741417</v>
+        <v>741110</v>
       </c>
       <c r="R39" t="n">
-        <v>7294498</v>
+        <v>7294497</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4886,17 +4938,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4911,27 +4968,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365365</t>
+          <t>https://artportalen.se/Sighting/135825121</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132365428</v>
+        <v>135825127</v>
       </c>
       <c r="B40" t="n">
-        <v>57975</v>
+        <v>78477</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4939,45 +4996,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Väster om Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741294</v>
+        <v>741118</v>
       </c>
       <c r="R40" t="n">
-        <v>7294330</v>
+        <v>7294382</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5001,17 +5050,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Flera ringhack på tall</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5026,24 +5080,24 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365428</t>
+          <t>https://artportalen.se/Sighting/135825127</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132365494</v>
+        <v>131421821</v>
       </c>
       <c r="B41" t="n">
         <v>57975</v>
@@ -5072,27 +5126,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>SydVäst om Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741247</v>
+        <v>741194</v>
       </c>
       <c r="R41" t="n">
-        <v>7294318</v>
+        <v>7294285</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5126,14 +5172,14 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Flertalet ringhack på träd i direkt anslutning till bohålet</t>
+          <t>Ringhack färska och gamla, tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
@@ -5141,27 +5187,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365494</t>
+          <t>https://artportalen.se/Sighting/131421821</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135825133</v>
+        <v>131421823</v>
       </c>
       <c r="B42" t="n">
-        <v>58006</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5189,14 +5235,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>741176</v>
+        <v>741167</v>
       </c>
       <c r="R42" t="n">
-        <v>7294442</v>
+        <v>7294289</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5223,27 +5269,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>20:17</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>20:17</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack</t>
+          <t>Nya och gamla ringhack rikligt, tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5269,16 +5305,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825133</t>
+          <t>https://artportalen.se/Sighting/131421823</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135828227</v>
+        <v>131421824</v>
       </c>
       <c r="B43" t="n">
-        <v>58006</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5304,24 +5340,16 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>741122</v>
+        <v>741275</v>
       </c>
       <c r="R43" t="n">
-        <v>7294378</v>
+        <v>7294333</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5348,27 +5376,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>19:58</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>19:58</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gamla och nya ringhack, tallhed.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5379,51 +5397,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828227</t>
+          <t>https://artportalen.se/Sighting/131421824</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135828230</v>
+        <v>131421825</v>
       </c>
       <c r="B44" t="n">
-        <v>58006</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5449,24 +5447,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>741155</v>
+        <v>741401</v>
       </c>
       <c r="R44" t="n">
-        <v>7294379</v>
+        <v>7294510</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5493,27 +5483,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>20:06</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>20:06</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Nya och gamla ringhack, rikligt, tall.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5524,51 +5504,31 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828230</t>
+          <t>https://artportalen.se/Sighting/131421825</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135828231</v>
+        <v>132365365</v>
       </c>
       <c r="B45" t="n">
-        <v>58006</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5604,17 +5564,17 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Väster om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>741186</v>
+        <v>741417</v>
       </c>
       <c r="R45" t="n">
-        <v>7294423</v>
+        <v>7294498</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5638,22 +5598,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>20:11</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>20:11</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5669,11 +5619,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5683,65 +5628,68 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828231</t>
+          <t>https://artportalen.se/Sighting/132365365</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135825126</v>
+        <v>132365428</v>
       </c>
       <c r="B46" t="n">
-        <v>57193</v>
+        <v>57975</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Väster om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>741114</v>
+        <v>741294</v>
       </c>
       <c r="R46" t="n">
-        <v>7294391</v>
+        <v>7294330</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5765,22 +5713,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>19:48</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>19:48</t>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5795,27 +5738,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825126</t>
+          <t>https://artportalen.se/Sighting/132365428</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135857317</v>
+        <v>132365494</v>
       </c>
       <c r="B47" t="n">
-        <v>58167</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5823,21 +5766,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5845,23 +5788,23 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>SydVäst om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>741177</v>
+        <v>741247</v>
       </c>
       <c r="R47" t="n">
-        <v>7294392</v>
+        <v>7294318</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5885,42 +5828,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>20:09</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>20:09</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Lockläten</t>
+          <t>Flertalet ringhack på träd i direkt anslutning till bohålet</t>
         </is>
       </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5930,39 +5858,39 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135857317</t>
+          <t>https://artportalen.se/Sighting/132365494</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131421826</v>
+        <v>135825133</v>
       </c>
       <c r="B48" t="n">
-        <v>58131</v>
+        <v>58006</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103023</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5973,14 +5901,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>741150</v>
+        <v>741176</v>
       </c>
       <c r="R48" t="n">
-        <v>7294265</v>
+        <v>7294442</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6007,12 +5935,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6038,33 +5981,33 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421826</t>
+          <t>https://artportalen.se/Sighting/135825133</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132365028</v>
+        <v>135828227</v>
       </c>
       <c r="B49" t="n">
-        <v>58131</v>
+        <v>58006</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103023</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6072,36 +6015,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>SydVäst om Sikträsket, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>741151</v>
+        <v>741122</v>
       </c>
       <c r="R49" t="n">
-        <v>7294262</v>
+        <v>7294378</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6125,22 +6060,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6151,6 +6091,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6160,22 +6120,22 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365028</t>
+          <t>https://artportalen.se/Sighting/135828227</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>110044410</v>
+        <v>135828230</v>
       </c>
       <c r="B50" t="n">
-        <v>58057</v>
+        <v>58006</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6183,16 +6143,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6201,19 +6161,27 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>741267</v>
+        <v>741155</v>
       </c>
       <c r="R50" t="n">
-        <v>7294536</v>
+        <v>7294379</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6237,12 +6205,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6253,59 +6236,83 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044410</t>
+          <t>https://artportalen.se/Sighting/135828230</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135828221</v>
+        <v>135828231</v>
       </c>
       <c r="B51" t="n">
-        <v>98204</v>
+        <v>58006</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6313,13 +6320,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>741098</v>
+        <v>741186</v>
       </c>
       <c r="R51" t="n">
-        <v>7294366</v>
+        <v>7294423</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6348,7 +6355,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6358,7 +6365,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6367,7 +6379,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6390,58 +6401,59 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828221</t>
+          <t>https://artportalen.se/Sighting/135828231</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129000540</v>
+        <v>135825126</v>
       </c>
       <c r="B52" t="n">
-        <v>79085</v>
+        <v>57193</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>741238</v>
+        <v>741114</v>
       </c>
       <c r="R52" t="n">
-        <v>7294334</v>
+        <v>7294391</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6465,17 +6477,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6490,27 +6507,27 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000540</t>
+          <t>https://artportalen.se/Sighting/135825126</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135828224</v>
+        <v>135857317</v>
       </c>
       <c r="B53" t="n">
-        <v>79232</v>
+        <v>58167</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6518,26 +6535,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6545,13 +6567,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>741114</v>
+        <v>741177</v>
       </c>
       <c r="R53" t="n">
-        <v>7294379</v>
+        <v>7294392</v>
       </c>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6580,7 +6602,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6590,7 +6612,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Lockläten</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6599,7 +6626,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6622,51 +6648,51 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828224</t>
+          <t>https://artportalen.se/Sighting/135857317</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135825134</v>
+        <v>131421826</v>
       </c>
       <c r="B54" t="n">
-        <v>79496</v>
+        <v>58131</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>260591</v>
+        <v>103023</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>741168</v>
+        <v>741150</v>
       </c>
       <c r="R54" t="n">
-        <v>7294460</v>
+        <v>7294265</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6693,22 +6719,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>20:20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>20:20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6733,6 +6749,823 @@
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131421826</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132365028</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SydVäst om Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>741151</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7294262</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132365028</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>110044410</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Rävabacken Utv, Nb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>741267</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7294536</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110044410</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135828221</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98204</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>741098</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7294366</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828221</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129000540</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>741238</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7294334</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000540</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135828224</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79232</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>741114</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7294379</v>
+      </c>
+      <c r="S59" t="n">
+        <v>6</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828224</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>136759760</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>741121</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7294370</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136759760</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135825134</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79496</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Sv Sikträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>741168</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7294460</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135825134</t>
         </is>
@@ -6793,6 +7626,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>135828229</v>
       </c>
       <c r="B3" t="n">
-        <v>83453</v>
+        <v>83455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>136759763</v>
       </c>
       <c r="B7" t="n">
-        <v>89371</v>
+        <v>89373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>135825122</v>
       </c>
       <c r="B8" t="n">
-        <v>92028</v>
+        <v>92033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>136759782</v>
       </c>
       <c r="B12" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136759889</v>
       </c>
       <c r="B16" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136759878</v>
       </c>
       <c r="B24" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>136759879</v>
       </c>
       <c r="B25" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>136760079</v>
       </c>
       <c r="B28" t="n">
-        <v>93430</v>
+        <v>93435</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>136759760</v>
       </c>
       <c r="B60" t="n">
-        <v>91583</v>
+        <v>91585</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>136759763</v>
       </c>
       <c r="B7" t="n">
-        <v>89373</v>
+        <v>89375</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>135825122</v>
       </c>
       <c r="B8" t="n">
-        <v>92033</v>
+        <v>92035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>136759782</v>
       </c>
       <c r="B12" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136759889</v>
       </c>
       <c r="B16" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136759878</v>
       </c>
       <c r="B24" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>136759879</v>
       </c>
       <c r="B25" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>136760079</v>
       </c>
       <c r="B28" t="n">
-        <v>93435</v>
+        <v>93437</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>136759760</v>
       </c>
       <c r="B60" t="n">
-        <v>91585</v>
+        <v>91587</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ61"/>
+  <dimension ref="A1:AZ73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,7 +796,7 @@
         <v>135828229</v>
       </c>
       <c r="B3" t="n">
-        <v>83455</v>
+        <v>83459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>136759763</v>
       </c>
       <c r="B7" t="n">
-        <v>89375</v>
+        <v>89377</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>135825122</v>
       </c>
       <c r="B8" t="n">
-        <v>92035</v>
+        <v>92037</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>136759782</v>
       </c>
       <c r="B12" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136759889</v>
+        <v>136672290</v>
       </c>
       <c r="B16" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,24 +2297,20 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741177</v>
+        <v>741440</v>
       </c>
       <c r="R16" t="n">
-        <v>7294519</v>
+        <v>7294605</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2338,27 +2334,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Ragg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,33 +2363,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759889</t>
+          <t>https://artportalen.se/Sighting/136672290</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110044379</v>
+        <v>136759889</v>
       </c>
       <c r="B17" t="n">
-        <v>93197</v>
+        <v>93407</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,37 +2398,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741287</v>
+        <v>741177</v>
       </c>
       <c r="R17" t="n">
-        <v>7294517</v>
+        <v>7294519</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2455,12 +2456,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2475,24 +2491,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044379</t>
+          <t>https://artportalen.se/Sighting/136759889</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129000536</v>
+        <v>110044379</v>
       </c>
       <c r="B18" t="n">
         <v>93197</v>
@@ -2520,21 +2536,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741464</v>
+        <v>741287</v>
       </c>
       <c r="R18" t="n">
-        <v>7294503</v>
+        <v>7294517</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2561,17 +2573,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,27 +2593,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000536</t>
+          <t>https://artportalen.se/Sighting/110044379</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135825120</v>
+        <v>129000536</v>
       </c>
       <c r="B19" t="n">
-        <v>93400</v>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,20 +2638,24 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741122</v>
+        <v>741464</v>
       </c>
       <c r="R19" t="n">
-        <v>7294512</v>
+        <v>7294503</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2668,22 +2679,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>18:58</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>18:58</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,27 +2704,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825120</t>
+          <t>https://artportalen.se/Sighting/129000536</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135825130</v>
+        <v>135825120</v>
       </c>
       <c r="B20" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2750,10 +2756,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741149</v>
+        <v>741122</v>
       </c>
       <c r="R20" t="n">
-        <v>7294363</v>
+        <v>7294512</v>
       </c>
       <c r="S20" t="n">
         <v>6</v>
@@ -2785,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2795,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2821,13 +2827,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825130</t>
+          <t>https://artportalen.se/Sighting/135825120</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135825132</v>
+        <v>135825130</v>
       </c>
       <c r="B21" t="n">
         <v>93399</v>
@@ -2862,10 +2868,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741186</v>
+        <v>741149</v>
       </c>
       <c r="R21" t="n">
-        <v>7294441</v>
+        <v>7294363</v>
       </c>
       <c r="S21" t="n">
         <v>6</v>
@@ -2897,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2907,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2933,16 +2939,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825132</t>
+          <t>https://artportalen.se/Sighting/135825130</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135828222</v>
+        <v>135825132</v>
       </c>
       <c r="B22" t="n">
-        <v>93400</v>
+        <v>93399</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2968,22 +2974,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741097</v>
+        <v>741186</v>
       </c>
       <c r="R22" t="n">
-        <v>7294374</v>
+        <v>7294441</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3012,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3022,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,36 +3034,30 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828222</t>
+          <t>https://artportalen.se/Sighting/135825132</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135828226</v>
+        <v>135828222</v>
       </c>
       <c r="B23" t="n">
         <v>93400</v>
@@ -3098,13 +3095,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>741113</v>
+        <v>741097</v>
       </c>
       <c r="R23" t="n">
-        <v>7294382</v>
+        <v>7294374</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3133,7 +3130,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3143,7 +3140,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3175,16 +3172,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828226</t>
+          <t>https://artportalen.se/Sighting/135828222</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136759878</v>
+        <v>135828226</v>
       </c>
       <c r="B24" t="n">
-        <v>93411</v>
+        <v>93400</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3209,24 +3206,23 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741257</v>
+        <v>741113</v>
       </c>
       <c r="R24" t="n">
-        <v>7294543</v>
+        <v>7294382</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3250,27 +3246,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3279,33 +3270,39 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759878</t>
+          <t>https://artportalen.se/Sighting/135828226</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136759879</v>
+        <v>136672292</v>
       </c>
       <c r="B25" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3330,21 +3327,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741265</v>
+        <v>741428</v>
       </c>
       <c r="R25" t="n">
-        <v>7294548</v>
+        <v>7294557</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3371,27 +3364,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3406,27 +3394,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759879</t>
+          <t>https://artportalen.se/Sighting/136672292</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129000539</v>
+        <v>136672298</v>
       </c>
       <c r="B26" t="n">
-        <v>93209</v>
+        <v>93413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3434,41 +3422,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>741260</v>
+        <v>741395</v>
       </c>
       <c r="R26" t="n">
-        <v>7294367</v>
+        <v>7294505</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3492,17 +3476,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3517,27 +3506,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000539</t>
+          <t>https://artportalen.se/Sighting/136672298</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129000541</v>
+        <v>136672300</v>
       </c>
       <c r="B27" t="n">
-        <v>93209</v>
+        <v>93413</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3545,41 +3534,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>741209</v>
+        <v>741423</v>
       </c>
       <c r="R27" t="n">
-        <v>7294469</v>
+        <v>7294498</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3603,17 +3588,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3628,27 +3618,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000541</t>
+          <t>https://artportalen.se/Sighting/136672300</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136760079</v>
+        <v>136759878</v>
       </c>
       <c r="B28" t="n">
-        <v>93437</v>
+        <v>93413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,37 +3646,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741170</v>
+        <v>741257</v>
       </c>
       <c r="R28" t="n">
-        <v>7294500</v>
+        <v>7294543</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3713,9 +3707,19 @@
           <t>2026-09-17</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3746,47 +3750,55 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136760079</t>
+          <t>https://artportalen.se/Sighting/136759878</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135825125</v>
+        <v>136759879</v>
       </c>
       <c r="B29" t="n">
-        <v>93429</v>
+        <v>93413</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741107</v>
+        <v>741265</v>
       </c>
       <c r="R29" t="n">
-        <v>7294391</v>
+        <v>7294548</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3813,27 +3825,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>och äldre fruktkropp</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3848,65 +3860,69 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825125</t>
+          <t>https://artportalen.se/Sighting/136759879</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135825123</v>
+        <v>129000539</v>
       </c>
       <c r="B30" t="n">
-        <v>91461</v>
+        <v>93209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5685</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>741088</v>
+        <v>741260</v>
       </c>
       <c r="R30" t="n">
-        <v>7294391</v>
+        <v>7294367</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3930,22 +3946,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>19:33</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>19:33</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3960,27 +3971,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825123</t>
+          <t>https://artportalen.se/Sighting/129000539</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129000537</v>
+        <v>129000541</v>
       </c>
       <c r="B31" t="n">
-        <v>93235</v>
+        <v>93209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3988,21 +3999,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4016,10 +4027,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>741430</v>
+        <v>741209</v>
       </c>
       <c r="R31" t="n">
-        <v>7294484</v>
+        <v>7294469</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4082,51 +4093,51 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000537</t>
+          <t>https://artportalen.se/Sighting/129000541</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131421831</v>
+        <v>136672294</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>93057</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>741264</v>
+        <v>741373</v>
       </c>
       <c r="R32" t="n">
-        <v>7294336</v>
+        <v>7294592</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4153,12 +4164,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4184,54 +4205,54 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421831</t>
+          <t>https://artportalen.se/Sighting/136672294</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131421828</v>
+        <v>136672299</v>
       </c>
       <c r="B33" t="n">
-        <v>79397</v>
+        <v>90709</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6434</v>
+        <v>4962</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741410</v>
+        <v>741424</v>
       </c>
       <c r="R33" t="n">
-        <v>7294501</v>
+        <v>7294497</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4255,12 +4276,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4286,57 +4317,54 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421828</t>
+          <t>https://artportalen.se/Sighting/136672299</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135828228</v>
+        <v>136760079</v>
       </c>
       <c r="B34" t="n">
-        <v>79498</v>
+        <v>93439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6434</v>
+        <v>5448</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741122</v>
+        <v>741170</v>
       </c>
       <c r="R34" t="n">
-        <v>7294378</v>
+        <v>7294500</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4360,22 +4388,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>19:58</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>19:58</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4384,78 +4407,53 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828228</t>
+          <t>https://artportalen.se/Sighting/136760079</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135825128</v>
+        <v>135825125</v>
       </c>
       <c r="B35" t="n">
-        <v>78876</v>
+        <v>93429</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>5449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4463,10 +4461,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741118</v>
+        <v>741107</v>
       </c>
       <c r="R35" t="n">
-        <v>7294382</v>
+        <v>7294391</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4498,7 +4496,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4508,7 +4506,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>och äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4534,58 +4537,54 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825128</t>
+          <t>https://artportalen.se/Sighting/135825125</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129000543</v>
+        <v>135825123</v>
       </c>
       <c r="B36" t="n">
-        <v>79084</v>
+        <v>91461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>5685</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741337</v>
+        <v>741088</v>
       </c>
       <c r="R36" t="n">
-        <v>7294536</v>
+        <v>7294391</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4609,17 +4608,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4634,27 +4638,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000543</t>
+          <t>https://artportalen.se/Sighting/135825123</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129000542</v>
+        <v>129000537</v>
       </c>
       <c r="B37" t="n">
-        <v>79946</v>
+        <v>93235</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4662,21 +4666,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4690,10 +4694,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>741225</v>
+        <v>741430</v>
       </c>
       <c r="R37" t="n">
-        <v>7294470</v>
+        <v>7294484</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4756,58 +4760,54 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000542</t>
+          <t>https://artportalen.se/Sighting/129000537</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129000544</v>
+        <v>136672302</v>
       </c>
       <c r="B38" t="n">
-        <v>79946</v>
+        <v>93397</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6055</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741341</v>
+        <v>741403</v>
       </c>
       <c r="R38" t="n">
-        <v>7294535</v>
+        <v>7294461</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4831,17 +4831,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4856,62 +4861,62 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000544</t>
+          <t>https://artportalen.se/Sighting/136672302</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135825121</v>
+        <v>136672295</v>
       </c>
       <c r="B39" t="n">
-        <v>80093</v>
+        <v>90897</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741110</v>
+        <v>741374</v>
       </c>
       <c r="R39" t="n">
-        <v>7294497</v>
+        <v>7294569</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4938,22 +4943,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4979,54 +4984,54 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825121</t>
+          <t>https://artportalen.se/Sighting/136672295</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135825127</v>
+        <v>131421831</v>
       </c>
       <c r="B40" t="n">
-        <v>78477</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741118</v>
+        <v>741264</v>
       </c>
       <c r="R40" t="n">
-        <v>7294382</v>
+        <v>7294336</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5050,22 +5055,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>19:55</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>19:55</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5091,38 +5086,38 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825127</t>
+          <t>https://artportalen.se/Sighting/131421831</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131421821</v>
+        <v>131421828</v>
       </c>
       <c r="B41" t="n">
-        <v>57975</v>
+        <v>79397</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5132,10 +5127,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741194</v>
+        <v>741410</v>
       </c>
       <c r="R41" t="n">
-        <v>7294285</v>
+        <v>7294501</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5170,11 +5165,6 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack färska och gamla, tall</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5198,51 +5188,54 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421821</t>
+          <t>https://artportalen.se/Sighting/131421828</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131421823</v>
+        <v>135828228</v>
       </c>
       <c r="B42" t="n">
-        <v>57975</v>
+        <v>79498</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>741167</v>
+        <v>741122</v>
       </c>
       <c r="R42" t="n">
-        <v>7294289</v>
+        <v>7294378</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5269,17 +5262,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Nya och gamla ringhack rikligt, tall</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5288,33 +5286,54 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421823</t>
+          <t>https://artportalen.se/Sighting/135828228</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131421824</v>
+        <v>135825128</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>78876</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5322,34 +5341,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>741275</v>
+        <v>741118</v>
       </c>
       <c r="R43" t="n">
-        <v>7294333</v>
+        <v>7294382</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5376,17 +5395,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gamla och nya ringhack, tallhed.</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5412,16 +5436,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421824</t>
+          <t>https://artportalen.se/Sighting/135825128</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131421825</v>
+        <v>129000543</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5429,37 +5453,41 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>741401</v>
+        <v>741337</v>
       </c>
       <c r="R44" t="n">
-        <v>7294510</v>
+        <v>7294536</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5483,17 +5511,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Nya och gamla ringhack, rikligt, tall.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5508,27 +5536,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421825</t>
+          <t>https://artportalen.se/Sighting/129000543</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132365365</v>
+        <v>129000542</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>79946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5536,45 +5564,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Väster om Sikträsket, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>741417</v>
+        <v>741225</v>
       </c>
       <c r="R45" t="n">
-        <v>7294498</v>
+        <v>7294470</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5598,17 +5622,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5623,27 +5647,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365365</t>
+          <t>https://artportalen.se/Sighting/129000542</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132365428</v>
+        <v>129000544</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>79946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5651,45 +5675,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Väster om Sikträsket, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>741294</v>
+        <v>741341</v>
       </c>
       <c r="R46" t="n">
-        <v>7294330</v>
+        <v>7294535</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5713,17 +5733,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Flera ringhack på tall</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5738,27 +5758,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365428</t>
+          <t>https://artportalen.se/Sighting/129000544</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132365494</v>
+        <v>135825121</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>80093</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5766,45 +5786,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>SydVäst om Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>741247</v>
+        <v>741110</v>
       </c>
       <c r="R47" t="n">
-        <v>7294318</v>
+        <v>7294497</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5828,24 +5840,29 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Flertalet ringhack på träd i direkt anslutning till bohålet</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="b">
         <v>0</v>
@@ -5853,27 +5870,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365494</t>
+          <t>https://artportalen.se/Sighting/135825121</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135825133</v>
+        <v>135825127</v>
       </c>
       <c r="B48" t="n">
-        <v>58006</v>
+        <v>78477</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5881,21 +5898,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5905,13 +5922,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>741176</v>
+        <v>741118</v>
       </c>
       <c r="R48" t="n">
-        <v>7294442</v>
+        <v>7294382</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5940,7 +5957,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5950,12 +5967,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:17</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska och gamla ringhack</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5981,16 +5993,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825133</t>
+          <t>https://artportalen.se/Sighting/135825127</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135828227</v>
+        <v>131421821</v>
       </c>
       <c r="B49" t="n">
-        <v>58006</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6016,24 +6028,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>741122</v>
+        <v>741194</v>
       </c>
       <c r="R49" t="n">
-        <v>7294378</v>
+        <v>7294285</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6060,27 +6064,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>19:58</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>19:58</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack färska och gamla, tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6091,51 +6085,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828227</t>
+          <t>https://artportalen.se/Sighting/131421821</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135828230</v>
+        <v>131421823</v>
       </c>
       <c r="B50" t="n">
-        <v>58006</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6161,24 +6135,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>741155</v>
+        <v>741167</v>
       </c>
       <c r="R50" t="n">
-        <v>7294379</v>
+        <v>7294289</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6205,27 +6171,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>20:06</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>20:06</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Nya och gamla ringhack rikligt, tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6236,51 +6192,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828230</t>
+          <t>https://artportalen.se/Sighting/131421823</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135828231</v>
+        <v>131421824</v>
       </c>
       <c r="B51" t="n">
-        <v>58006</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6306,27 +6242,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>741186</v>
+        <v>741275</v>
       </c>
       <c r="R51" t="n">
-        <v>7294423</v>
+        <v>7294333</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6350,27 +6278,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>20:11</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>20:11</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gamla och nya ringhack, tallhed.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6381,79 +6299,69 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828231</t>
+          <t>https://artportalen.se/Sighting/131421824</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135825126</v>
+        <v>131421825</v>
       </c>
       <c r="B52" t="n">
-        <v>57193</v>
+        <v>57975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>741114</v>
+        <v>741401</v>
       </c>
       <c r="R52" t="n">
-        <v>7294391</v>
+        <v>7294510</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6477,22 +6385,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>19:48</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>19:48</t>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Nya och gamla ringhack, rikligt, tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6518,16 +6421,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825126</t>
+          <t>https://artportalen.se/Sighting/131421825</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135857317</v>
+        <v>132365365</v>
       </c>
       <c r="B53" t="n">
-        <v>58167</v>
+        <v>57975</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6535,21 +6438,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6557,23 +6460,23 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Väster om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>741177</v>
+        <v>741417</v>
       </c>
       <c r="R53" t="n">
-        <v>7294392</v>
+        <v>7294498</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6597,27 +6500,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>20:09</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>20:09</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Lockläten</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6628,11 +6521,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6642,39 +6530,39 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135857317</t>
+          <t>https://artportalen.se/Sighting/132365365</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131421826</v>
+        <v>132365428</v>
       </c>
       <c r="B54" t="n">
-        <v>58131</v>
+        <v>57975</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103023</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6683,19 +6571,27 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Väster om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>741150</v>
+        <v>741294</v>
       </c>
       <c r="R54" t="n">
-        <v>7294265</v>
+        <v>7294330</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6725,6 +6621,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6739,44 +6640,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421826</t>
+          <t>https://artportalen.se/Sighting/132365428</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132365028</v>
+        <v>132365494</v>
       </c>
       <c r="B55" t="n">
-        <v>58131</v>
+        <v>57975</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103023</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6784,36 +6685,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>SydVäst om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>741151</v>
+        <v>741247</v>
       </c>
       <c r="R55" t="n">
-        <v>7294262</v>
+        <v>7294318</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6840,26 +6733,21 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:02</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Flertalet ringhack på träd i direkt anslutning till bohålet</t>
         </is>
       </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG55" t="b">
         <v>0</v>
@@ -6878,16 +6766,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365028</t>
+          <t>https://artportalen.se/Sighting/132365494</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>110044410</v>
+        <v>135825133</v>
       </c>
       <c r="B56" t="n">
-        <v>58057</v>
+        <v>58006</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6895,16 +6783,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6915,17 +6803,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>741267</v>
+        <v>741176</v>
       </c>
       <c r="R56" t="n">
-        <v>7294536</v>
+        <v>7294442</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6949,12 +6837,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6969,55 +6872,59 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044410</t>
+          <t>https://artportalen.se/Sighting/135825133</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135828221</v>
+        <v>135828227</v>
       </c>
       <c r="B57" t="n">
-        <v>98204</v>
+        <v>58006</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7025,10 +6932,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>741098</v>
+        <v>741122</v>
       </c>
       <c r="R57" t="n">
-        <v>7294366</v>
+        <v>7294378</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7060,7 +6967,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7070,7 +6977,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7079,13 +6991,27 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
           <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7102,16 +7028,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828221</t>
+          <t>https://artportalen.se/Sighting/135828227</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129000540</v>
+        <v>135828230</v>
       </c>
       <c r="B58" t="n">
-        <v>79085</v>
+        <v>58006</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7119,41 +7045,45 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>741238</v>
+        <v>741155</v>
       </c>
       <c r="R58" t="n">
-        <v>7294334</v>
+        <v>7294379</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7177,17 +7107,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7198,31 +7138,51 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000540</t>
+          <t>https://artportalen.se/Sighting/135828230</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135828224</v>
+        <v>135828231</v>
       </c>
       <c r="B59" t="n">
-        <v>79232</v>
+        <v>58006</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7230,26 +7190,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7257,10 +7222,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>741114</v>
+        <v>741186</v>
       </c>
       <c r="R59" t="n">
-        <v>7294379</v>
+        <v>7294423</v>
       </c>
       <c r="S59" t="n">
         <v>6</v>
@@ -7292,7 +7257,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7302,7 +7267,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7311,7 +7281,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7334,58 +7303,59 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828224</t>
+          <t>https://artportalen.se/Sighting/135828231</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136759760</v>
+        <v>135825126</v>
       </c>
       <c r="B60" t="n">
-        <v>91587</v>
+        <v>57193</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>256703</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>741121</v>
+        <v>741114</v>
       </c>
       <c r="R60" t="n">
-        <v>7294370</v>
+        <v>7294391</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7409,27 +7379,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:49</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7444,27 +7409,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759760</t>
+          <t>https://artportalen.se/Sighting/135825126</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135825134</v>
+        <v>135857317</v>
       </c>
       <c r="B61" t="n">
-        <v>79496</v>
+        <v>58167</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7472,34 +7437,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>260591</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>741168</v>
+        <v>741177</v>
       </c>
       <c r="R61" t="n">
-        <v>7294460</v>
+        <v>7294392</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7531,7 +7504,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7541,7 +7514,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Lockläten</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7552,22 +7530,1395 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135857317</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>131421826</v>
+      </c>
+      <c r="B62" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Sarvasvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>741150</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7294265</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131421826</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>132365028</v>
+      </c>
+      <c r="B63" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SydVäst om Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>741151</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7294262</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132365028</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>110044410</v>
+      </c>
+      <c r="B64" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Rävabacken Utv, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>741267</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7294536</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110044410</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>136672291</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98227</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>741439</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7294564</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136672291</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135828221</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98204</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>741098</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7294366</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828221</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129000540</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>741238</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7294334</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000540</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135828224</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79232</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>741114</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7294379</v>
+      </c>
+      <c r="S68" t="n">
+        <v>6</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828224</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>136672303</v>
+      </c>
+      <c r="B69" t="n">
+        <v>93444</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>741408</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7294460</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136672303</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>136759760</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91589</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>741121</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7294370</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136759760</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135825134</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79496</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Sv Sikträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>741168</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7294460</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135825134</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>136672289</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>741425</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7294608</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136672289</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>136672293</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>741420</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7294551</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136672293</t>
         </is>
       </c>
     </row>
@@ -7633,6 +8984,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>135828229</v>
       </c>
       <c r="B3" t="n">
-        <v>83459</v>
+        <v>83461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>136759763</v>
       </c>
       <c r="B7" t="n">
-        <v>89377</v>
+        <v>89379</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>135825122</v>
       </c>
       <c r="B8" t="n">
-        <v>92037</v>
+        <v>92039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>136759782</v>
       </c>
       <c r="B12" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136672290</v>
       </c>
       <c r="B16" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136759889</v>
       </c>
       <c r="B17" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136672292</v>
       </c>
       <c r="B25" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136672298</v>
       </c>
       <c r="B26" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136672300</v>
       </c>
       <c r="B27" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136759878</v>
       </c>
       <c r="B28" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>136759879</v>
       </c>
       <c r="B29" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>136672294</v>
       </c>
       <c r="B32" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>136672299</v>
       </c>
       <c r="B33" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>136760079</v>
       </c>
       <c r="B34" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>136672302</v>
       </c>
       <c r="B38" t="n">
-        <v>93397</v>
+        <v>93399</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>136672295</v>
       </c>
       <c r="B39" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>136672291</v>
       </c>
       <c r="B65" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>136672303</v>
       </c>
       <c r="B69" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>136759760</v>
       </c>
       <c r="B70" t="n">
-        <v>91589</v>
+        <v>91591</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>136672289</v>
       </c>
       <c r="B72" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>136672293</v>
       </c>
       <c r="B73" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>135828229</v>
       </c>
       <c r="B3" t="n">
-        <v>83461</v>
+        <v>83462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>136759763</v>
       </c>
       <c r="B7" t="n">
-        <v>89379</v>
+        <v>89380</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>136759782</v>
       </c>
       <c r="B12" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136672290</v>
       </c>
       <c r="B16" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136759889</v>
       </c>
       <c r="B17" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136672292</v>
       </c>
       <c r="B25" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136672298</v>
       </c>
       <c r="B26" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136672300</v>
       </c>
       <c r="B27" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136759878</v>
       </c>
       <c r="B28" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>136759879</v>
       </c>
       <c r="B29" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>136672294</v>
       </c>
       <c r="B32" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>136672299</v>
       </c>
       <c r="B33" t="n">
-        <v>90711</v>
+        <v>90712</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>136760079</v>
       </c>
       <c r="B34" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>136672302</v>
       </c>
       <c r="B38" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>136672295</v>
       </c>
       <c r="B39" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>136672291</v>
       </c>
       <c r="B65" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>136672303</v>
       </c>
       <c r="B69" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>136759760</v>
       </c>
       <c r="B70" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>136672289</v>
       </c>
       <c r="B72" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>136672293</v>
       </c>
       <c r="B73" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>136759763</v>
       </c>
       <c r="B7" t="n">
-        <v>89380</v>
+        <v>89386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>136759782</v>
       </c>
       <c r="B12" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136672290</v>
       </c>
       <c r="B16" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136759889</v>
       </c>
       <c r="B17" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136672292</v>
       </c>
       <c r="B25" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136672298</v>
       </c>
       <c r="B26" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136672300</v>
       </c>
       <c r="B27" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136759878</v>
       </c>
       <c r="B28" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>136759879</v>
       </c>
       <c r="B29" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>136672294</v>
       </c>
       <c r="B32" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>136672299</v>
       </c>
       <c r="B33" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>136760079</v>
       </c>
       <c r="B34" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>136672302</v>
       </c>
       <c r="B38" t="n">
-        <v>93400</v>
+        <v>93406</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>136672295</v>
       </c>
       <c r="B39" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>136672291</v>
       </c>
       <c r="B65" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>136672303</v>
       </c>
       <c r="B69" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>136759760</v>
       </c>
       <c r="B70" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>135828229</v>
       </c>
       <c r="B3" t="n">
-        <v>83462</v>
+        <v>83466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>136759763</v>
       </c>
       <c r="B7" t="n">
-        <v>89386</v>
+        <v>89390</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>136759782</v>
       </c>
       <c r="B12" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136672290</v>
       </c>
       <c r="B16" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136759889</v>
       </c>
       <c r="B17" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136672292</v>
       </c>
       <c r="B25" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136672298</v>
       </c>
       <c r="B26" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136672300</v>
       </c>
       <c r="B27" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136759878</v>
       </c>
       <c r="B28" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>136759879</v>
       </c>
       <c r="B29" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>136672294</v>
       </c>
       <c r="B32" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>136672299</v>
       </c>
       <c r="B33" t="n">
-        <v>90718</v>
+        <v>90722</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>136760079</v>
       </c>
       <c r="B34" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>136672302</v>
       </c>
       <c r="B38" t="n">
-        <v>93406</v>
+        <v>93410</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>136672295</v>
       </c>
       <c r="B39" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>136672291</v>
       </c>
       <c r="B65" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>136672303</v>
       </c>
       <c r="B69" t="n">
-        <v>93453</v>
+        <v>93457</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>136759760</v>
       </c>
       <c r="B70" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>136672289</v>
       </c>
       <c r="B72" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>136672293</v>
       </c>
       <c r="B73" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -7891,7 +7891,7 @@
         <v>136672291</v>
       </c>
       <c r="B65" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>135828229</v>
       </c>
       <c r="B3" t="n">
-        <v>83466</v>
+        <v>83468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>136759763</v>
       </c>
       <c r="B7" t="n">
-        <v>89390</v>
+        <v>89392</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>136759782</v>
       </c>
       <c r="B12" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136672290</v>
       </c>
       <c r="B16" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136759889</v>
       </c>
       <c r="B17" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136672292</v>
       </c>
       <c r="B25" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136672298</v>
       </c>
       <c r="B26" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136672300</v>
       </c>
       <c r="B27" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136759878</v>
       </c>
       <c r="B28" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>136759879</v>
       </c>
       <c r="B29" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>136672294</v>
       </c>
       <c r="B32" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>136672299</v>
       </c>
       <c r="B33" t="n">
-        <v>90722</v>
+        <v>90724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>136760079</v>
       </c>
       <c r="B34" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>136672302</v>
       </c>
       <c r="B38" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>136672295</v>
       </c>
       <c r="B39" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>136672291</v>
       </c>
       <c r="B65" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>136672303</v>
       </c>
       <c r="B69" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>136759760</v>
       </c>
       <c r="B70" t="n">
-        <v>91602</v>
+        <v>91604</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>136672289</v>
       </c>
       <c r="B72" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>136672293</v>
       </c>
       <c r="B73" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>135828229</v>
       </c>
       <c r="B3" t="n">
-        <v>83468</v>
+        <v>83481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>136759763</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
+        <v>89405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>136759782</v>
       </c>
       <c r="B12" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136672290</v>
       </c>
       <c r="B16" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136759889</v>
       </c>
       <c r="B17" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136672292</v>
       </c>
       <c r="B25" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136672298</v>
       </c>
       <c r="B26" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136672300</v>
       </c>
       <c r="B27" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136759878</v>
       </c>
       <c r="B28" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>136759879</v>
       </c>
       <c r="B29" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>136672294</v>
       </c>
       <c r="B32" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>136672299</v>
       </c>
       <c r="B33" t="n">
-        <v>90724</v>
+        <v>90737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>136760079</v>
       </c>
       <c r="B34" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>136672302</v>
       </c>
       <c r="B38" t="n">
-        <v>93412</v>
+        <v>93425</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>136672295</v>
       </c>
       <c r="B39" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>136672291</v>
       </c>
       <c r="B65" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>136672303</v>
       </c>
       <c r="B69" t="n">
-        <v>93459</v>
+        <v>93472</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>136759760</v>
       </c>
       <c r="B70" t="n">
-        <v>91604</v>
+        <v>91617</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>136672289</v>
       </c>
       <c r="B72" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>136672293</v>
       </c>
       <c r="B73" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>135828229</v>
       </c>
       <c r="B3" t="n">
-        <v>83481</v>
+        <v>83483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>136759763</v>
       </c>
       <c r="B7" t="n">
-        <v>89405</v>
+        <v>89407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>136759782</v>
       </c>
       <c r="B12" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136672290</v>
       </c>
       <c r="B16" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136759889</v>
       </c>
       <c r="B17" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136672292</v>
       </c>
       <c r="B25" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136672298</v>
       </c>
       <c r="B26" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136672300</v>
       </c>
       <c r="B27" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136759878</v>
       </c>
       <c r="B28" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>136759879</v>
       </c>
       <c r="B29" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>136672294</v>
       </c>
       <c r="B32" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>136672299</v>
       </c>
       <c r="B33" t="n">
-        <v>90737</v>
+        <v>90739</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>136760079</v>
       </c>
       <c r="B34" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>136672302</v>
       </c>
       <c r="B38" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>136672295</v>
       </c>
       <c r="B39" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>136672291</v>
       </c>
       <c r="B65" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>136672303</v>
       </c>
       <c r="B69" t="n">
-        <v>93472</v>
+        <v>93473</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>136759760</v>
       </c>
       <c r="B70" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>136672289</v>
       </c>
       <c r="B72" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>136672293</v>
       </c>
       <c r="B73" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>136759763</v>
       </c>
       <c r="B7" t="n">
-        <v>89407</v>
+        <v>89410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>136759782</v>
       </c>
       <c r="B12" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136672290</v>
       </c>
       <c r="B16" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136759889</v>
       </c>
       <c r="B17" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136672292</v>
       </c>
       <c r="B25" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136672298</v>
       </c>
       <c r="B26" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136672300</v>
       </c>
       <c r="B27" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136759878</v>
       </c>
       <c r="B28" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>136759879</v>
       </c>
       <c r="B29" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>136672294</v>
       </c>
       <c r="B32" t="n">
-        <v>93087</v>
+        <v>93090</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>136672299</v>
       </c>
       <c r="B33" t="n">
-        <v>90739</v>
+        <v>90742</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>136760079</v>
       </c>
       <c r="B34" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>136672302</v>
       </c>
       <c r="B38" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>136672295</v>
       </c>
       <c r="B39" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>136672291</v>
       </c>
       <c r="B65" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>136672303</v>
       </c>
       <c r="B69" t="n">
-        <v>93473</v>
+        <v>93476</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>136759760</v>
       </c>
       <c r="B70" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>136759763</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
+        <v>89420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>136759782</v>
       </c>
       <c r="B12" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136672290</v>
       </c>
       <c r="B16" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136759889</v>
       </c>
       <c r="B17" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136672292</v>
       </c>
       <c r="B25" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136672298</v>
       </c>
       <c r="B26" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136672300</v>
       </c>
       <c r="B27" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136759878</v>
       </c>
       <c r="B28" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>136759879</v>
       </c>
       <c r="B29" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>136672294</v>
       </c>
       <c r="B32" t="n">
-        <v>93090</v>
+        <v>93100</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>136672299</v>
       </c>
       <c r="B33" t="n">
-        <v>90742</v>
+        <v>90752</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>136760079</v>
       </c>
       <c r="B34" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>136672302</v>
       </c>
       <c r="B38" t="n">
-        <v>93429</v>
+        <v>93439</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>136672295</v>
       </c>
       <c r="B39" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>136672291</v>
       </c>
       <c r="B65" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>136672303</v>
       </c>
       <c r="B69" t="n">
-        <v>93476</v>
+        <v>93486</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>136759760</v>
       </c>
       <c r="B70" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>136672289</v>
       </c>
       <c r="B72" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>136672293</v>
       </c>
       <c r="B73" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>136759763</v>
       </c>
       <c r="B7" t="n">
-        <v>89420</v>
+        <v>89421</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>136759782</v>
       </c>
       <c r="B12" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136672290</v>
       </c>
       <c r="B16" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>136759889</v>
       </c>
       <c r="B17" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136672292</v>
       </c>
       <c r="B25" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136672298</v>
       </c>
       <c r="B26" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136672300</v>
       </c>
       <c r="B27" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>136759878</v>
       </c>
       <c r="B28" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>136759879</v>
       </c>
       <c r="B29" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>136672294</v>
       </c>
       <c r="B32" t="n">
-        <v>93100</v>
+        <v>93101</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>136672299</v>
       </c>
       <c r="B33" t="n">
-        <v>90752</v>
+        <v>90753</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>136760079</v>
       </c>
       <c r="B34" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>136672302</v>
       </c>
       <c r="B38" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>136672295</v>
       </c>
       <c r="B39" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>136672291</v>
       </c>
       <c r="B65" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>136672303</v>
       </c>
       <c r="B69" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>136759760</v>
       </c>
       <c r="B70" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -2272,7 +2272,7 @@
         <v>136672290</v>
       </c>
       <c r="B16" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136672292</v>
       </c>
       <c r="B25" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136672298</v>
       </c>
       <c r="B26" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136672300</v>
       </c>
       <c r="B27" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>136672294</v>
       </c>
       <c r="B32" t="n">
-        <v>93101</v>
+        <v>93104</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>136672299</v>
       </c>
       <c r="B33" t="n">
-        <v>90753</v>
+        <v>90756</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>136672302</v>
       </c>
       <c r="B38" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>136672295</v>
       </c>
       <c r="B39" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>136672291</v>
       </c>
       <c r="B65" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>136672303</v>
       </c>
       <c r="B69" t="n">
-        <v>93487</v>
+        <v>93492</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>136672289</v>
       </c>
       <c r="B72" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>136672293</v>
       </c>
       <c r="B73" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -2272,7 +2272,7 @@
         <v>136672290</v>
       </c>
       <c r="B16" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>136672292</v>
       </c>
       <c r="B25" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>136672298</v>
       </c>
       <c r="B26" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>136672300</v>
       </c>
       <c r="B27" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>136672294</v>
       </c>
       <c r="B32" t="n">
-        <v>93104</v>
+        <v>93106</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>136672302</v>
       </c>
       <c r="B38" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>136672295</v>
       </c>
       <c r="B39" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>136672291</v>
       </c>
       <c r="B65" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>136672303</v>
       </c>
       <c r="B69" t="n">
-        <v>93492</v>
+        <v>93494</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ73"/>
+  <dimension ref="A1:AZ88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135825129</v>
+        <v>136672305</v>
       </c>
       <c r="B2" t="n">
-        <v>83453</v>
+        <v>79553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741142</v>
+        <v>741346</v>
       </c>
       <c r="R2" t="n">
-        <v>7294368</v>
+        <v>7294438</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,16 +786,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825129</t>
+          <t>https://artportalen.se/Sighting/136672305</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135828229</v>
+        <v>135825129</v>
       </c>
       <c r="B3" t="n">
-        <v>83483</v>
+        <v>83453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,17 +823,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741140</v>
+        <v>741142</v>
       </c>
       <c r="R3" t="n">
-        <v>7294373</v>
+        <v>7294368</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,27 +888,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828229</t>
+          <t>https://artportalen.se/Sighting/135825129</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135825124</v>
+        <v>135828229</v>
       </c>
       <c r="B4" t="n">
-        <v>79140</v>
+        <v>83483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,34 +916,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741095</v>
+        <v>741140</v>
       </c>
       <c r="R4" t="n">
-        <v>7294406</v>
+        <v>7294373</v>
       </c>
       <c r="S4" t="n">
         <v>6</v>
@@ -976,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,74 +994,72 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825124</t>
+          <t>https://artportalen.se/Sighting/135828229</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131421827</v>
+        <v>135825124</v>
       </c>
       <c r="B5" t="n">
-        <v>79442</v>
+        <v>79140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>639</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grenlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Evernia mesomorpha</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741351</v>
+        <v>741095</v>
       </c>
       <c r="R5" t="n">
-        <v>7294438</v>
+        <v>7294406</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,12 +1083,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,7 +1107,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1118,16 +1124,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421827</t>
+          <t>https://artportalen.se/Sighting/135825124</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135828232</v>
+        <v>131421827</v>
       </c>
       <c r="B6" t="n">
-        <v>89369</v>
+        <v>79442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,45 +1141,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>816</v>
+        <v>639</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smultronkantarell</t>
+          <t>Grenlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Aphroditeola olida</t>
+          <t>Evernia mesomorpha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741170</v>
+        <v>741351</v>
       </c>
       <c r="R6" t="n">
-        <v>7294518</v>
+        <v>7294438</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1200,22 +1198,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>20:26</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>20:26</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,35 +1216,30 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828232</t>
+          <t>https://artportalen.se/Sighting/131421827</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136759763</v>
+        <v>135828232</v>
       </c>
       <c r="B7" t="n">
-        <v>89421</v>
+        <v>89369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,22 +1266,29 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741169</v>
+        <v>741170</v>
       </c>
       <c r="R7" t="n">
-        <v>7294502</v>
+        <v>7294518</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,27 +1312,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,74 +1336,81 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759763</t>
+          <t>https://artportalen.se/Sighting/135828232</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135825122</v>
+        <v>136759763</v>
       </c>
       <c r="B8" t="n">
-        <v>92039</v>
+        <v>89421</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3242</v>
+        <v>816</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741077</v>
+        <v>741169</v>
       </c>
       <c r="R8" t="n">
-        <v>7294449</v>
+        <v>7294502</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,22 +1434,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,80 +1463,68 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825122</t>
+          <t>https://artportalen.se/Sighting/136759763</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135828223</v>
+        <v>136672310</v>
       </c>
       <c r="B9" t="n">
-        <v>87497</v>
+        <v>93485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3690</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Soop</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741105</v>
+        <v>741344</v>
       </c>
       <c r="R9" t="n">
-        <v>7294388</v>
+        <v>7294415</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,22 +1551,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,39 +1575,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828223</t>
+          <t>https://artportalen.se/Sighting/136672310</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110044413</v>
+        <v>135825122</v>
       </c>
       <c r="B10" t="n">
-        <v>93189</v>
+        <v>92039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,37 +1609,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741238</v>
+        <v>741077</v>
       </c>
       <c r="R10" t="n">
-        <v>7294539</v>
+        <v>7294449</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1684,12 +1666,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,33 +1690,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044413</t>
+          <t>https://artportalen.se/Sighting/135825122</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135825131</v>
+        <v>135828223</v>
       </c>
       <c r="B11" t="n">
-        <v>93391</v>
+        <v>87497</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,34 +1725,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741193</v>
+        <v>741105</v>
       </c>
       <c r="R11" t="n">
-        <v>7294441</v>
+        <v>7294388</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1791,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1805,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,33 +1814,39 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825131</t>
+          <t>https://artportalen.se/Sighting/135828223</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136759782</v>
+        <v>110044413</v>
       </c>
       <c r="B12" t="n">
-        <v>93448</v>
+        <v>93189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,24 +1871,20 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741380</v>
+        <v>741238</v>
       </c>
       <c r="R12" t="n">
-        <v>7294626</v>
+        <v>7294539</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1902,27 +1908,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>07:56</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>07:56</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,27 +1928,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759782</t>
+          <t>https://artportalen.se/Sighting/110044413</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110044367</v>
+        <v>135825131</v>
       </c>
       <c r="B13" t="n">
-        <v>93191</v>
+        <v>93391</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,37 +1956,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741263</v>
+        <v>741193</v>
       </c>
       <c r="R13" t="n">
-        <v>7294543</v>
+        <v>7294441</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,12 +2010,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,27 +2040,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044367</t>
+          <t>https://artportalen.se/Sighting/135825131</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110044387</v>
+        <v>136672316</v>
       </c>
       <c r="B14" t="n">
-        <v>93191</v>
+        <v>93461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,37 +2068,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741505</v>
+        <v>741287</v>
       </c>
       <c r="R14" t="n">
-        <v>7294450</v>
+        <v>7294442</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2121,12 +2122,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,27 +2152,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044387</t>
+          <t>https://artportalen.se/Sighting/136672316</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129000538</v>
+        <v>136672318</v>
       </c>
       <c r="B15" t="n">
-        <v>93191</v>
+        <v>93461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2169,41 +2180,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741402</v>
+        <v>741266</v>
       </c>
       <c r="R15" t="n">
-        <v>7294418</v>
+        <v>7294463</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2227,17 +2234,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,27 +2264,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000538</t>
+          <t>https://artportalen.se/Sighting/136672318</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136672290</v>
+        <v>136672324</v>
       </c>
       <c r="B16" t="n">
-        <v>93457</v>
+        <v>93461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,21 +2292,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2304,13 +2316,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741440</v>
+        <v>741352</v>
       </c>
       <c r="R16" t="n">
-        <v>7294605</v>
+        <v>7294586</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2339,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2349,12 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:53</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ragg</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,7 +2370,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2381,16 +2387,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136672290</t>
+          <t>https://artportalen.se/Sighting/136672324</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136759889</v>
+        <v>136759782</v>
       </c>
       <c r="B17" t="n">
-        <v>93450</v>
+        <v>93448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2398,21 +2404,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2426,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741177</v>
+        <v>741380</v>
       </c>
       <c r="R17" t="n">
-        <v>7294519</v>
+        <v>7294626</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2461,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,7 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2502,16 +2508,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759889</t>
+          <t>https://artportalen.se/Sighting/136759782</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110044379</v>
+        <v>110044367</v>
       </c>
       <c r="B18" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2519,21 +2525,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2543,10 +2549,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741287</v>
+        <v>741263</v>
       </c>
       <c r="R18" t="n">
-        <v>7294517</v>
+        <v>7294543</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2604,16 +2610,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044379</t>
+          <t>https://artportalen.se/Sighting/110044367</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129000536</v>
+        <v>110044387</v>
       </c>
       <c r="B19" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,38 +2627,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741464</v>
+        <v>741505</v>
       </c>
       <c r="R19" t="n">
-        <v>7294503</v>
+        <v>7294450</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2679,17 +2681,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,27 +2701,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000536</t>
+          <t>https://artportalen.se/Sighting/110044387</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135825120</v>
+        <v>129000538</v>
       </c>
       <c r="B20" t="n">
-        <v>93400</v>
+        <v>93191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,37 +2729,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741122</v>
+        <v>741402</v>
       </c>
       <c r="R20" t="n">
-        <v>7294512</v>
+        <v>7294418</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2786,22 +2787,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>18:58</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>18:58</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2816,27 +2812,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825120</t>
+          <t>https://artportalen.se/Sighting/129000538</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135825130</v>
+        <v>136672290</v>
       </c>
       <c r="B21" t="n">
-        <v>93399</v>
+        <v>93463</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,34 +2840,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741149</v>
+        <v>741440</v>
       </c>
       <c r="R21" t="n">
-        <v>7294363</v>
+        <v>7294605</v>
       </c>
       <c r="S21" t="n">
         <v>6</v>
@@ -2898,22 +2894,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ragg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,6 +2923,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2939,16 +2941,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825130</t>
+          <t>https://artportalen.se/Sighting/136672290</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135825132</v>
+        <v>136759889</v>
       </c>
       <c r="B22" t="n">
-        <v>93399</v>
+        <v>93450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2956,37 +2958,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741186</v>
+        <v>741177</v>
       </c>
       <c r="R22" t="n">
-        <v>7294441</v>
+        <v>7294519</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3010,22 +3016,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,27 +3051,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825132</t>
+          <t>https://artportalen.se/Sighting/136759889</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135828222</v>
+        <v>110044379</v>
       </c>
       <c r="B23" t="n">
-        <v>93400</v>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,22 +3097,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Rävabacken Utv, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>741097</v>
+        <v>741287</v>
       </c>
       <c r="R23" t="n">
-        <v>7294374</v>
+        <v>7294517</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3125,22 +3133,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>19:37</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>19:37</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,39 +3147,33 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828222</t>
+          <t>https://artportalen.se/Sighting/110044379</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135828226</v>
+        <v>129000536</v>
       </c>
       <c r="B24" t="n">
-        <v>93400</v>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,23 +3198,24 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741113</v>
+        <v>741464</v>
       </c>
       <c r="R24" t="n">
-        <v>7294382</v>
+        <v>7294503</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3246,22 +3239,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>19:56</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>19:56</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,39 +3258,33 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828226</t>
+          <t>https://artportalen.se/Sighting/129000536</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136672292</v>
+        <v>135825120</v>
       </c>
       <c r="B25" t="n">
-        <v>93463</v>
+        <v>93400</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3330,17 +3312,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741428</v>
+        <v>741122</v>
       </c>
       <c r="R25" t="n">
-        <v>7294557</v>
+        <v>7294512</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3364,22 +3346,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3405,16 +3387,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136672292</t>
+          <t>https://artportalen.se/Sighting/135825120</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136672298</v>
+        <v>135825130</v>
       </c>
       <c r="B26" t="n">
-        <v>93463</v>
+        <v>93399</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3442,17 +3424,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>741395</v>
+        <v>741149</v>
       </c>
       <c r="R26" t="n">
-        <v>7294505</v>
+        <v>7294363</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3476,22 +3458,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3517,16 +3499,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136672298</t>
+          <t>https://artportalen.se/Sighting/135825130</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136672300</v>
+        <v>135825132</v>
       </c>
       <c r="B27" t="n">
-        <v>93463</v>
+        <v>93399</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,17 +3536,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>741423</v>
+        <v>741186</v>
       </c>
       <c r="R27" t="n">
-        <v>7294498</v>
+        <v>7294441</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3588,22 +3570,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3629,16 +3611,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136672300</t>
+          <t>https://artportalen.se/Sighting/135825132</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136759878</v>
+        <v>135828222</v>
       </c>
       <c r="B28" t="n">
-        <v>93456</v>
+        <v>93400</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3663,24 +3645,23 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>741257</v>
+        <v>741097</v>
       </c>
       <c r="R28" t="n">
-        <v>7294543</v>
+        <v>7294374</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3704,27 +3685,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3733,33 +3709,39 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759878</t>
+          <t>https://artportalen.se/Sighting/135828222</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136759879</v>
+        <v>135828226</v>
       </c>
       <c r="B29" t="n">
-        <v>93456</v>
+        <v>93400</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,24 +3766,23 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>741265</v>
+        <v>741113</v>
       </c>
       <c r="R29" t="n">
-        <v>7294548</v>
+        <v>7294382</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3825,27 +3806,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3854,33 +3830,39 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759879</t>
+          <t>https://artportalen.se/Sighting/135828226</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129000539</v>
+        <v>136672292</v>
       </c>
       <c r="B30" t="n">
-        <v>93209</v>
+        <v>93469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3888,41 +3870,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>741260</v>
+        <v>741428</v>
       </c>
       <c r="R30" t="n">
-        <v>7294367</v>
+        <v>7294557</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3946,17 +3924,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,27 +3954,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000539</t>
+          <t>https://artportalen.se/Sighting/136672292</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129000541</v>
+        <v>136672298</v>
       </c>
       <c r="B31" t="n">
-        <v>93209</v>
+        <v>93469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3999,41 +3982,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>741209</v>
+        <v>741395</v>
       </c>
       <c r="R31" t="n">
-        <v>7294469</v>
+        <v>7294505</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4057,17 +4036,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4082,27 +4066,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000541</t>
+          <t>https://artportalen.se/Sighting/136672298</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136672294</v>
+        <v>136672300</v>
       </c>
       <c r="B32" t="n">
-        <v>93106</v>
+        <v>93469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4110,21 +4094,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4134,10 +4118,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>741373</v>
+        <v>741423</v>
       </c>
       <c r="R32" t="n">
-        <v>7294592</v>
+        <v>7294498</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4169,7 +4153,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4179,7 +4163,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4205,16 +4189,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136672294</t>
+          <t>https://artportalen.se/Sighting/136672300</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136672299</v>
+        <v>136672306</v>
       </c>
       <c r="B33" t="n">
-        <v>90756</v>
+        <v>93469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4222,21 +4206,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4246,13 +4230,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>741424</v>
+        <v>741344</v>
       </c>
       <c r="R33" t="n">
-        <v>7294497</v>
+        <v>7294430</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4281,7 +4265,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4291,7 +4275,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4317,16 +4301,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136672299</t>
+          <t>https://artportalen.se/Sighting/136672306</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136760079</v>
+        <v>136672313</v>
       </c>
       <c r="B34" t="n">
-        <v>93482</v>
+        <v>93469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,37 +4318,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>741170</v>
+        <v>741326</v>
       </c>
       <c r="R34" t="n">
-        <v>7294500</v>
+        <v>7294425</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4388,17 +4372,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4413,58 +4402,62 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136760079</t>
+          <t>https://artportalen.se/Sighting/136672313</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135825125</v>
+        <v>136672319</v>
       </c>
       <c r="B35" t="n">
-        <v>93429</v>
+        <v>93469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>741107</v>
+        <v>741255</v>
       </c>
       <c r="R35" t="n">
-        <v>7294391</v>
+        <v>7294525</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4491,27 +4484,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>och äldre fruktkropp</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4537,54 +4525,58 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825125</t>
+          <t>https://artportalen.se/Sighting/136672319</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135825123</v>
+        <v>136759878</v>
       </c>
       <c r="B36" t="n">
-        <v>91461</v>
+        <v>93456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>741088</v>
+        <v>741257</v>
       </c>
       <c r="R36" t="n">
-        <v>7294391</v>
+        <v>7294543</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4608,22 +4600,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4638,27 +4635,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825123</t>
+          <t>https://artportalen.se/Sighting/136759878</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129000537</v>
+        <v>136759879</v>
       </c>
       <c r="B37" t="n">
-        <v>93235</v>
+        <v>93456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,21 +4663,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4694,13 +4691,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>741430</v>
+        <v>741265</v>
       </c>
       <c r="R37" t="n">
-        <v>7294484</v>
+        <v>7294548</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4724,12 +4721,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4760,16 +4767,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000537</t>
+          <t>https://artportalen.se/Sighting/136759879</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136672302</v>
+        <v>136672325</v>
       </c>
       <c r="B38" t="n">
-        <v>93447</v>
+        <v>93473</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4777,21 +4784,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6055</v>
+        <v>4365</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4801,10 +4808,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>741403</v>
+        <v>741351</v>
       </c>
       <c r="R38" t="n">
-        <v>7294461</v>
+        <v>7294598</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4836,7 +4843,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4846,7 +4853,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4872,54 +4879,58 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136672302</t>
+          <t>https://artportalen.se/Sighting/136672325</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136672295</v>
+        <v>129000539</v>
       </c>
       <c r="B39" t="n">
-        <v>90946</v>
+        <v>93209</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6286</v>
+        <v>4366</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sikträsket, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>741374</v>
+        <v>741260</v>
       </c>
       <c r="R39" t="n">
-        <v>7294569</v>
+        <v>7294367</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4943,22 +4954,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>17:12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>17:12</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4973,65 +4979,69 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136672295</t>
+          <t>https://artportalen.se/Sighting/129000539</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131421831</v>
+        <v>129000541</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>93209</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>741264</v>
+        <v>741209</v>
       </c>
       <c r="R40" t="n">
-        <v>7294336</v>
+        <v>7294469</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5055,12 +5065,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5075,62 +5090,62 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421831</t>
+          <t>https://artportalen.se/Sighting/129000541</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131421828</v>
+        <v>136672294</v>
       </c>
       <c r="B41" t="n">
-        <v>79397</v>
+        <v>93112</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6434</v>
+        <v>4745</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>741410</v>
+        <v>741373</v>
       </c>
       <c r="R41" t="n">
-        <v>7294501</v>
+        <v>7294592</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5157,12 +5172,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5188,54 +5213,51 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421828</t>
+          <t>https://artportalen.se/Sighting/136672294</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135828228</v>
+        <v>136672307</v>
       </c>
       <c r="B42" t="n">
-        <v>79498</v>
+        <v>93112</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6434</v>
+        <v>4745</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>741122</v>
+        <v>741347</v>
       </c>
       <c r="R42" t="n">
-        <v>7294378</v>
+        <v>7294428</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5262,22 +5284,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5286,54 +5308,33 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828228</t>
+          <t>https://artportalen.se/Sighting/136672307</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135825128</v>
+        <v>136672320</v>
       </c>
       <c r="B43" t="n">
-        <v>78876</v>
+        <v>93112</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5341,34 +5342,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6437</v>
+        <v>4745</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>741118</v>
+        <v>741347</v>
       </c>
       <c r="R43" t="n">
-        <v>7294382</v>
+        <v>7294548</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5395,22 +5396,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5436,16 +5437,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825128</t>
+          <t>https://artportalen.se/Sighting/136672320</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129000543</v>
+        <v>136672299</v>
       </c>
       <c r="B44" t="n">
-        <v>79084</v>
+        <v>90761</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5453,41 +5454,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>4962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>741337</v>
+        <v>741424</v>
       </c>
       <c r="R44" t="n">
-        <v>7294536</v>
+        <v>7294497</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5511,17 +5508,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5536,27 +5538,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000543</t>
+          <t>https://artportalen.se/Sighting/136672299</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129000542</v>
+        <v>136672309</v>
       </c>
       <c r="B45" t="n">
-        <v>79946</v>
+        <v>90761</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5564,41 +5566,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>4962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>741225</v>
+        <v>741345</v>
       </c>
       <c r="R45" t="n">
-        <v>7294470</v>
+        <v>7294420</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5622,17 +5620,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5647,27 +5650,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000542</t>
+          <t>https://artportalen.se/Sighting/136672309</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129000544</v>
+        <v>136672323</v>
       </c>
       <c r="B46" t="n">
-        <v>79946</v>
+        <v>90761</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5675,41 +5678,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>4962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>741341</v>
+        <v>741352</v>
       </c>
       <c r="R46" t="n">
-        <v>7294535</v>
+        <v>7294578</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5733,17 +5732,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5758,27 +5762,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000544</t>
+          <t>https://artportalen.se/Sighting/136672323</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135825121</v>
+        <v>136672304</v>
       </c>
       <c r="B47" t="n">
-        <v>80093</v>
+        <v>93495</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5786,34 +5790,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>741110</v>
+        <v>741408</v>
       </c>
       <c r="R47" t="n">
-        <v>7294497</v>
+        <v>7294460</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5840,22 +5847,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5864,6 +5871,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5881,16 +5889,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825121</t>
+          <t>https://artportalen.se/Sighting/136672304</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135825127</v>
+        <v>136672322</v>
       </c>
       <c r="B48" t="n">
-        <v>78477</v>
+        <v>93495</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,37 +5906,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6487</v>
+        <v>5448</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>741118</v>
+        <v>741348</v>
       </c>
       <c r="R48" t="n">
-        <v>7294382</v>
+        <v>7294569</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5952,22 +5960,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5993,16 +6001,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825127</t>
+          <t>https://artportalen.se/Sighting/136672322</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131421821</v>
+        <v>136760079</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>93482</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,37 +6018,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5448</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>741194</v>
+        <v>741170</v>
       </c>
       <c r="R49" t="n">
-        <v>7294285</v>
+        <v>7294500</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6064,17 +6072,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack färska och gamla, tall</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6089,62 +6097,58 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421821</t>
+          <t>https://artportalen.se/Sighting/136760079</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131421823</v>
+        <v>135825125</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>93429</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>741167</v>
+        <v>741107</v>
       </c>
       <c r="R50" t="n">
-        <v>7294289</v>
+        <v>7294391</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6171,17 +6175,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Nya och gamla ringhack rikligt, tall</t>
+          <t>och äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6207,54 +6221,54 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421823</t>
+          <t>https://artportalen.se/Sighting/135825125</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131421824</v>
+        <v>135825123</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>91461</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5685</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>741275</v>
+        <v>741088</v>
       </c>
       <c r="R51" t="n">
-        <v>7294333</v>
+        <v>7294391</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6278,17 +6292,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Gamla och nya ringhack, tallhed.</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6314,16 +6333,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421824</t>
+          <t>https://artportalen.se/Sighting/135825123</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131421825</v>
+        <v>129000537</v>
       </c>
       <c r="B52" t="n">
-        <v>57975</v>
+        <v>93235</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6331,37 +6350,41 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>741401</v>
+        <v>741430</v>
       </c>
       <c r="R52" t="n">
-        <v>7294510</v>
+        <v>7294484</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6385,17 +6408,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Nya och gamla ringhack, rikligt, tall.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6410,73 +6433,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421825</t>
+          <t>https://artportalen.se/Sighting/129000537</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132365365</v>
+        <v>136672302</v>
       </c>
       <c r="B53" t="n">
-        <v>57975</v>
+        <v>93453</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6055</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Väster om Sikträsket, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>741417</v>
+        <v>741403</v>
       </c>
       <c r="R53" t="n">
-        <v>7294498</v>
+        <v>7294461</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6500,17 +6515,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6525,73 +6545,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365365</t>
+          <t>https://artportalen.se/Sighting/136672302</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132365428</v>
+        <v>136672295</v>
       </c>
       <c r="B54" t="n">
-        <v>57975</v>
+        <v>90951</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Väster om Sikträsket, Nb</t>
+          <t>Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>741294</v>
+        <v>741374</v>
       </c>
       <c r="R54" t="n">
-        <v>7294330</v>
+        <v>7294569</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6615,17 +6627,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Flera ringhack på tall</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6640,73 +6657,65 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365428</t>
+          <t>https://artportalen.se/Sighting/136672295</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132365494</v>
+        <v>131421831</v>
       </c>
       <c r="B55" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>SydVäst om Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>741247</v>
+        <v>741264</v>
       </c>
       <c r="R55" t="n">
-        <v>7294318</v>
+        <v>7294336</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6738,16 +6747,11 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Flertalet ringhack på träd i direkt anslutning till bohålet</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="b">
         <v>0</v>
@@ -6755,62 +6759,62 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365494</t>
+          <t>https://artportalen.se/Sighting/131421831</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135825133</v>
+        <v>131421828</v>
       </c>
       <c r="B56" t="n">
-        <v>58006</v>
+        <v>79397</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>741176</v>
+        <v>741410</v>
       </c>
       <c r="R56" t="n">
-        <v>7294442</v>
+        <v>7294501</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6837,27 +6841,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>20:17</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>20:17</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska och gamla ringhack</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6883,48 +6872,43 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825133</t>
+          <t>https://artportalen.se/Sighting/131421828</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135828227</v>
+        <v>135828228</v>
       </c>
       <c r="B57" t="n">
-        <v>58006</v>
+        <v>79498</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6980,17 +6964,13 @@
           <t>19:58</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7028,16 +7008,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828227</t>
+          <t>https://artportalen.se/Sighting/135828228</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135828230</v>
+        <v>135825128</v>
       </c>
       <c r="B58" t="n">
-        <v>58006</v>
+        <v>78876</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7045,42 +7025,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>741155</v>
+        <v>741118</v>
       </c>
       <c r="R58" t="n">
-        <v>7294379</v>
+        <v>7294382</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7112,7 +7084,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7122,12 +7094,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:06</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7138,51 +7105,31 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828230</t>
+          <t>https://artportalen.se/Sighting/135825128</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135828231</v>
+        <v>129000543</v>
       </c>
       <c r="B59" t="n">
-        <v>58006</v>
+        <v>79084</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7190,45 +7137,41 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>741186</v>
+        <v>741337</v>
       </c>
       <c r="R59" t="n">
-        <v>7294423</v>
+        <v>7294536</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7252,27 +7195,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>20:11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>20:11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7283,79 +7216,73 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828231</t>
+          <t>https://artportalen.se/Sighting/129000543</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135825126</v>
+        <v>129000542</v>
       </c>
       <c r="B60" t="n">
-        <v>57193</v>
+        <v>79946</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sv Sikträskberget, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>741114</v>
+        <v>741225</v>
       </c>
       <c r="R60" t="n">
-        <v>7294391</v>
+        <v>7294470</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7379,22 +7306,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>19:48</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>19:48</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7409,27 +7331,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825126</t>
+          <t>https://artportalen.se/Sighting/129000542</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135857317</v>
+        <v>129000544</v>
       </c>
       <c r="B61" t="n">
-        <v>58167</v>
+        <v>79946</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7437,45 +7359,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Grundsel, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>741177</v>
+        <v>741341</v>
       </c>
       <c r="R61" t="n">
-        <v>7294392</v>
+        <v>7294535</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7499,27 +7417,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>20:09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>20:09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Lockläten</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7530,71 +7438,66 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135857317</t>
+          <t>https://artportalen.se/Sighting/129000544</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131421826</v>
+        <v>135825121</v>
       </c>
       <c r="B62" t="n">
-        <v>58131</v>
+        <v>80093</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103023</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sarvasvägen, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>741150</v>
+        <v>741110</v>
       </c>
       <c r="R62" t="n">
-        <v>7294265</v>
+        <v>7294497</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7621,12 +7524,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7652,70 +7565,54 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131421826</t>
+          <t>https://artportalen.se/Sighting/135825121</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132365028</v>
+        <v>135825127</v>
       </c>
       <c r="B63" t="n">
-        <v>58131</v>
+        <v>78477</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103023</v>
+        <v>6487</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>SydVäst om Sikträsket, Nb</t>
+          <t>Sv Sikträskberget, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>741151</v>
+        <v>741118</v>
       </c>
       <c r="R63" t="n">
-        <v>7294262</v>
+        <v>7294382</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7739,22 +7636,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7769,27 +7666,27 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132365028</t>
+          <t>https://artportalen.se/Sighting/135825127</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>110044410</v>
+        <v>131421821</v>
       </c>
       <c r="B64" t="n">
-        <v>58057</v>
+        <v>57975</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7797,16 +7694,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7817,17 +7714,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Rävabacken Utv, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>741267</v>
+        <v>741194</v>
       </c>
       <c r="R64" t="n">
-        <v>7294536</v>
+        <v>7294285</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7851,12 +7748,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack färska och gamla, tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7871,62 +7773,62 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110044410</t>
+          <t>https://artportalen.se/Sighting/131421821</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136672291</v>
+        <v>131421823</v>
       </c>
       <c r="B65" t="n">
-        <v>98280</v>
+        <v>57975</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>741439</v>
+        <v>741167</v>
       </c>
       <c r="R65" t="n">
-        <v>7294564</v>
+        <v>7294289</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7953,22 +7855,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:58</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:58</t>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Nya och gamla ringhack rikligt, tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7994,55 +7891,51 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136672291</t>
+          <t>https://artportalen.se/Sighting/131421823</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135828221</v>
+        <v>131421824</v>
       </c>
       <c r="B66" t="n">
-        <v>98204</v>
+        <v>57975</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>741098</v>
+        <v>741275</v>
       </c>
       <c r="R66" t="n">
-        <v>7294366</v>
+        <v>7294333</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8069,22 +7962,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>19:35</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>19:35</t>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Gamla och nya ringhack, tallhed.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8093,39 +7981,33 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828221</t>
+          <t>https://artportalen.se/Sighting/131421824</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129000540</v>
+        <v>131421825</v>
       </c>
       <c r="B67" t="n">
-        <v>79085</v>
+        <v>57975</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8133,41 +8015,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>Sarvasvägen, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>741238</v>
+        <v>741401</v>
       </c>
       <c r="R67" t="n">
-        <v>7294334</v>
+        <v>7294510</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8191,17 +8069,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Nya och gamla ringhack, rikligt, tall.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8216,27 +8094,27 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000540</t>
+          <t>https://artportalen.se/Sighting/131421825</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135828224</v>
+        <v>132365365</v>
       </c>
       <c r="B68" t="n">
-        <v>79232</v>
+        <v>57975</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8244,40 +8122,45 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>SV Sikträsket, Nb</t>
+          <t>Väster om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>741114</v>
+        <v>741417</v>
       </c>
       <c r="R68" t="n">
-        <v>7294379</v>
+        <v>7294498</v>
       </c>
       <c r="S68" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8301,22 +8184,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>19:50</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>19:50</t>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8325,14 +8203,8 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8342,60 +8214,68 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135828224</t>
+          <t>https://artportalen.se/Sighting/132365365</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136672303</v>
+        <v>132365428</v>
       </c>
       <c r="B69" t="n">
-        <v>93494</v>
+        <v>57975</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>232140</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sikträsket, Nb</t>
+          <t>Väster om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>741408</v>
+        <v>741294</v>
       </c>
       <c r="R69" t="n">
-        <v>7294460</v>
+        <v>7294330</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8419,22 +8299,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>17:38</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>17:38</t>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Flera ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8443,34 +8318,33 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136672303</t>
+          <t>https://artportalen.se/Sighting/132365428</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>136759760</v>
+        <v>132365494</v>
       </c>
       <c r="B70" t="n">
-        <v>91633</v>
+        <v>57975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8478,41 +8352,45 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>256703</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Grundsel, Nb</t>
+          <t>SydVäst om Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>741121</v>
+        <v>741247</v>
       </c>
       <c r="R70" t="n">
-        <v>7294370</v>
+        <v>7294318</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8536,34 +8414,24 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>08:49</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>08:49</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Flertalet ringhack på träd i direkt anslutning till bohålet</t>
         </is>
       </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG70" t="b">
         <v>0</v>
@@ -8571,27 +8439,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136759760</t>
+          <t>https://artportalen.se/Sighting/132365494</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135825134</v>
+        <v>135825133</v>
       </c>
       <c r="B71" t="n">
-        <v>79496</v>
+        <v>58006</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8599,21 +8467,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8623,10 +8491,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>741168</v>
+        <v>741176</v>
       </c>
       <c r="R71" t="n">
-        <v>7294460</v>
+        <v>7294442</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8658,7 +8526,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8668,7 +8536,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8694,16 +8567,16 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135825134</t>
+          <t>https://artportalen.se/Sighting/135825133</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>136672289</v>
+        <v>135828227</v>
       </c>
       <c r="B72" t="n">
-        <v>79539</v>
+        <v>58006</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8711,34 +8584,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sikträsket, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>741425</v>
+        <v>741122</v>
       </c>
       <c r="R72" t="n">
-        <v>7294608</v>
+        <v>7294378</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8765,22 +8646,27 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8791,31 +8677,51 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136672289</t>
+          <t>https://artportalen.se/Sighting/135828227</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>136672293</v>
+        <v>135828230</v>
       </c>
       <c r="B73" t="n">
-        <v>79539</v>
+        <v>58006</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8823,34 +8729,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sikträsket, Nb</t>
+          <t>SV Sikträsket, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>741420</v>
+        <v>741155</v>
       </c>
       <c r="R73" t="n">
-        <v>7294551</v>
+        <v>7294379</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8877,22 +8791,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8903,20 +8822,1785 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828230</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135828231</v>
+      </c>
+      <c r="B74" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>741186</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7294423</v>
+      </c>
+      <c r="S74" t="n">
+        <v>6</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828231</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135825126</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57193</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Sv Sikträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>741114</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7294391</v>
+      </c>
+      <c r="S75" t="n">
+        <v>6</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135825126</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135857317</v>
+      </c>
+      <c r="B76" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>741177</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7294392</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Lockläten</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135857317</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>131421826</v>
+      </c>
+      <c r="B77" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Sarvasvägen, Nb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>741150</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7294265</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131421826</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>132365028</v>
+      </c>
+      <c r="B78" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SydVäst om Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>741151</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7294262</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132365028</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>110044410</v>
+      </c>
+      <c r="B79" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Rävabacken Utv, Nb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>741267</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7294536</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110044410</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>136672291</v>
+      </c>
+      <c r="B80" t="n">
+        <v>98286</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>741439</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7294564</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136672291</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135828221</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98204</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>741098</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7294366</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828221</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129000540</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>741238</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7294334</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000540</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135828224</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79232</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SV Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>741114</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7294379</v>
+      </c>
+      <c r="S83" t="n">
+        <v>6</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135828224</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>136672303</v>
+      </c>
+      <c r="B84" t="n">
+        <v>93500</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>741408</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7294460</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136672303</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>136759760</v>
+      </c>
+      <c r="B85" t="n">
+        <v>91633</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Grundsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>741121</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7294370</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136759760</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135825134</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79496</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Sv Sikträskberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>741168</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7294460</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135825134</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>136672289</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79544</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>741425</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7294608</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136672289</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>136672293</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79544</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Sikträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>741420</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7294551</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136672293</t>
         </is>
@@ -8996,6 +10680,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136672305</v>
       </c>
       <c r="B2" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>136672310</v>
       </c>
       <c r="B9" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136672316</v>
       </c>
       <c r="B14" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>136672318</v>
       </c>
       <c r="B15" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>136672324</v>
       </c>
       <c r="B16" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136672290</v>
       </c>
       <c r="B21" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>136672292</v>
       </c>
       <c r="B30" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>136672298</v>
       </c>
       <c r="B31" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>136672300</v>
       </c>
       <c r="B32" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>136672306</v>
       </c>
       <c r="B33" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>136672313</v>
       </c>
       <c r="B34" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>136672319</v>
       </c>
       <c r="B35" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>136672325</v>
       </c>
       <c r="B38" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>136672294</v>
       </c>
       <c r="B41" t="n">
-        <v>93112</v>
+        <v>93124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>136672307</v>
       </c>
       <c r="B42" t="n">
-        <v>93112</v>
+        <v>93124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>136672320</v>
       </c>
       <c r="B43" t="n">
-        <v>93112</v>
+        <v>93124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>136672299</v>
       </c>
       <c r="B44" t="n">
-        <v>90761</v>
+        <v>90772</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>136672309</v>
       </c>
       <c r="B45" t="n">
-        <v>90761</v>
+        <v>90772</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136672323</v>
       </c>
       <c r="B46" t="n">
-        <v>90761</v>
+        <v>90772</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>136672304</v>
       </c>
       <c r="B47" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>136672322</v>
       </c>
       <c r="B48" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>136672302</v>
       </c>
       <c r="B53" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>136672295</v>
       </c>
       <c r="B54" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>136672291</v>
       </c>
       <c r="B80" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>136672303</v>
       </c>
       <c r="B84" t="n">
-        <v>93500</v>
+        <v>93512</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>136672289</v>
       </c>
       <c r="B87" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>136672293</v>
       </c>
       <c r="B88" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136672305</v>
       </c>
       <c r="B2" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>136672310</v>
       </c>
       <c r="B9" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136672316</v>
       </c>
       <c r="B14" t="n">
-        <v>93473</v>
+        <v>93474</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>136672318</v>
       </c>
       <c r="B15" t="n">
-        <v>93473</v>
+        <v>93474</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>136672324</v>
       </c>
       <c r="B16" t="n">
-        <v>93473</v>
+        <v>93474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136672290</v>
       </c>
       <c r="B21" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>136672292</v>
       </c>
       <c r="B30" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>136672298</v>
       </c>
       <c r="B31" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>136672300</v>
       </c>
       <c r="B32" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>136672306</v>
       </c>
       <c r="B33" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>136672313</v>
       </c>
       <c r="B34" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>136672319</v>
       </c>
       <c r="B35" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>136672325</v>
       </c>
       <c r="B38" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>136672294</v>
       </c>
       <c r="B41" t="n">
-        <v>93124</v>
+        <v>93125</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>136672307</v>
       </c>
       <c r="B42" t="n">
-        <v>93124</v>
+        <v>93125</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>136672320</v>
       </c>
       <c r="B43" t="n">
-        <v>93124</v>
+        <v>93125</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>136672299</v>
       </c>
       <c r="B44" t="n">
-        <v>90772</v>
+        <v>90773</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>136672309</v>
       </c>
       <c r="B45" t="n">
-        <v>90772</v>
+        <v>90773</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136672323</v>
       </c>
       <c r="B46" t="n">
-        <v>90772</v>
+        <v>90773</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>136672304</v>
       </c>
       <c r="B47" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>136672322</v>
       </c>
       <c r="B48" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>136672302</v>
       </c>
       <c r="B53" t="n">
-        <v>93465</v>
+        <v>93466</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>136672295</v>
       </c>
       <c r="B54" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>136672291</v>
       </c>
       <c r="B80" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>136672303</v>
       </c>
       <c r="B84" t="n">
-        <v>93512</v>
+        <v>93513</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>136672289</v>
       </c>
       <c r="B87" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>136672293</v>
       </c>
       <c r="B88" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136672305</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>136672310</v>
       </c>
       <c r="B9" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136672316</v>
       </c>
       <c r="B14" t="n">
-        <v>93474</v>
+        <v>93477</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>136672318</v>
       </c>
       <c r="B15" t="n">
-        <v>93474</v>
+        <v>93477</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>136672324</v>
       </c>
       <c r="B16" t="n">
-        <v>93474</v>
+        <v>93477</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136672290</v>
       </c>
       <c r="B21" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>136672292</v>
       </c>
       <c r="B30" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>136672298</v>
       </c>
       <c r="B31" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>136672300</v>
       </c>
       <c r="B32" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>136672306</v>
       </c>
       <c r="B33" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>136672313</v>
       </c>
       <c r="B34" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>136672319</v>
       </c>
       <c r="B35" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>136672325</v>
       </c>
       <c r="B38" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>136672294</v>
       </c>
       <c r="B41" t="n">
-        <v>93125</v>
+        <v>93128</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>136672307</v>
       </c>
       <c r="B42" t="n">
-        <v>93125</v>
+        <v>93128</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>136672320</v>
       </c>
       <c r="B43" t="n">
-        <v>93125</v>
+        <v>93128</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>136672299</v>
       </c>
       <c r="B44" t="n">
-        <v>90773</v>
+        <v>90776</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>136672309</v>
       </c>
       <c r="B45" t="n">
-        <v>90773</v>
+        <v>90776</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136672323</v>
       </c>
       <c r="B46" t="n">
-        <v>90773</v>
+        <v>90776</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>136672304</v>
       </c>
       <c r="B47" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>136672322</v>
       </c>
       <c r="B48" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>136672302</v>
       </c>
       <c r="B53" t="n">
-        <v>93466</v>
+        <v>93469</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>136672295</v>
       </c>
       <c r="B54" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>136672291</v>
       </c>
       <c r="B80" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>136672303</v>
       </c>
       <c r="B84" t="n">
-        <v>93513</v>
+        <v>93516</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>136672289</v>
       </c>
       <c r="B87" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>136672293</v>
       </c>
       <c r="B88" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 51047-2025 artfynd.xlsx
+++ b/artfynd/A 51047-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136672305</v>
       </c>
       <c r="B2" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>136672310</v>
       </c>
       <c r="B9" t="n">
-        <v>93501</v>
+        <v>93505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136672316</v>
       </c>
       <c r="B14" t="n">
-        <v>93477</v>
+        <v>93481</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>136672318</v>
       </c>
       <c r="B15" t="n">
-        <v>93477</v>
+        <v>93481</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>136672324</v>
       </c>
       <c r="B16" t="n">
-        <v>93477</v>
+        <v>93481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136672290</v>
       </c>
       <c r="B21" t="n">
-        <v>93479</v>
+        <v>93483</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>136672292</v>
       </c>
       <c r="B30" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>136672298</v>
       </c>
       <c r="B31" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>136672300</v>
       </c>
       <c r="B32" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>136672306</v>
       </c>
       <c r="B33" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>136672313</v>
       </c>
       <c r="B34" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>136672319</v>
       </c>
       <c r="B35" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>136672325</v>
       </c>
       <c r="B38" t="n">
-        <v>93489</v>
+        <v>93493</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>136672294</v>
       </c>
       <c r="B41" t="n">
-        <v>93128</v>
+        <v>93132</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>136672307</v>
       </c>
       <c r="B42" t="n">
-        <v>93128</v>
+        <v>93132</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>136672320</v>
       </c>
       <c r="B43" t="n">
-        <v>93128</v>
+        <v>93132</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>136672299</v>
       </c>
       <c r="B44" t="n">
-        <v>90776</v>
+        <v>90780</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>136672309</v>
       </c>
       <c r="B45" t="n">
-        <v>90776</v>
+        <v>90780</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>136672323</v>
       </c>
       <c r="B46" t="n">
-        <v>90776</v>
+        <v>90780</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>136672304</v>
       </c>
       <c r="B47" t="n">
-        <v>93511</v>
+        <v>93515</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>136672322</v>
       </c>
       <c r="B48" t="n">
-        <v>93511</v>
+        <v>93515</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>136672302</v>
       </c>
       <c r="B53" t="n">
-        <v>93469</v>
+        <v>93473</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>136672295</v>
       </c>
       <c r="B54" t="n">
-        <v>90967</v>
+        <v>90971</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>136672291</v>
       </c>
       <c r="B80" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>136672303</v>
       </c>
       <c r="B84" t="n">
-        <v>93516</v>
+        <v>93520</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>136672289</v>
       </c>
       <c r="B87" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>136672293</v>
       </c>
       <c r="B88" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
